--- a/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
+++ b/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\knn\Documents\hikr90\02.프로젝트\01.인트라넷\01.설계\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DAF2D6-F849-4F61-A2EE-8394086508D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7401C4AA-AFAA-4D59-A504-7E6CF4AC1755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="793" activeTab="9" xr2:uid="{B204C4DA-9ED1-4F0A-AC7E-C11DE778500E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="793" xr2:uid="{B204C4DA-9ED1-4F0A-AC7E-C11DE778500E}"/>
   </bookViews>
   <sheets>
     <sheet name="MENU" sheetId="8" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="279">
   <si>
     <t>EMP_IDX</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -553,10 +553,6 @@
   </si>
   <si>
     <t>기안 작성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>양식 관리</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1173,10 +1169,6 @@
     <t>STAT_0020</t>
   </si>
   <si>
-    <t>연차 공유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>intrAprvInqy4010.do</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1198,6 +1190,64 @@
   </si>
   <si>
     <t>N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOC_0010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOC_0020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOC_0030</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회의실 (대)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회의실 (중)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회의실 (소)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MENU_0030</t>
+  </si>
+  <si>
+    <t>intrTempInqy2010.do</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MENU_0031</t>
+  </si>
+  <si>
+    <t>내부규정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정 관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intrRegsInqy1010.do</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결재양식 관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결재양식 연동</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1622,7 +1672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60644FAD-9B99-49D5-B453-33EA3359146C}">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="15.625" style="2" customWidth="1"/>
@@ -1733,13 +1783,13 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>42</v>
@@ -1749,7 +1799,7 @@
       </c>
       <c r="H5" s="4"/>
       <c r="J5" s="3" t="str">
-        <f t="shared" ref="J5:J31" si="1">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A5&amp;"','"&amp;B5&amp;"','"&amp;C5&amp;"','"&amp;D5&amp;"','"&amp;E5&amp;"','"&amp;F5&amp;"','"&amp;G5&amp;"','"&amp;H5&amp;"');"</f>
+        <f t="shared" ref="J5:J33" si="1">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A5&amp;"','"&amp;B5&amp;"','"&amp;C5&amp;"','"&amp;D5&amp;"','"&amp;E5&amp;"','"&amp;F5&amp;"','"&amp;G5&amp;"','"&amp;H5&amp;"');"</f>
         <v>INSERT INTO MENU VALUES('MENU_0003','0','회의 관리','MENU_0001','intrMtgInqy1010.do','Y','3','');</v>
       </c>
     </row>
@@ -1761,13 +1811,13 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>42</v>
@@ -1777,8 +1827,8 @@
       </c>
       <c r="H6" s="4"/>
       <c r="J6" s="3" t="str">
-        <f t="shared" ref="J6" si="2">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A6&amp;"','"&amp;B6&amp;"','"&amp;C6&amp;"','"&amp;D6&amp;"','"&amp;E6&amp;"','"&amp;F6&amp;"','"&amp;G6&amp;"','"&amp;H6&amp;"');"</f>
-        <v>INSERT INTO MENU VALUES('MENU_0004','0','연차 공유','MENU_0001','intrAprvInqy3010.do','Y','4','');</v>
+        <f t="shared" si="1"/>
+        <v>INSERT INTO MENU VALUES('MENU_0004','0','일정 관리','MENU_0001','intrAprvInqy3010.do','Y','4','');</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1789,10 +1839,14 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+        <v>274</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>276</v>
+      </c>
       <c r="F7" s="4" t="s">
         <v>42</v>
       </c>
@@ -1801,8 +1855,8 @@
       </c>
       <c r="H7" s="4"/>
       <c r="J7" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0005','0','전자결재','','','Y','5','');</v>
+        <f t="shared" ref="J7" si="2">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A7&amp;"','"&amp;B7&amp;"','"&amp;C7&amp;"','"&amp;D7&amp;"','"&amp;E7&amp;"','"&amp;F7&amp;"','"&amp;G7&amp;"','"&amp;H7&amp;"');"</f>
+        <v>INSERT INTO MENU VALUES('MENU_0005','0','내부규정','MENU_0001','intrRegsInqy1010.do','Y','5','');</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1813,14 +1867,10 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
       <c r="F8" s="4" t="s">
         <v>42</v>
       </c>
@@ -1830,7 +1880,7 @@
       <c r="H8" s="4"/>
       <c r="J8" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0006','0','기안 작성','MENU_0005','intrAprvInqy1010.do','Y','6','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0006','0','전자결재','','','Y','6','');</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -1841,13 +1891,13 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>42</v>
@@ -1857,8 +1907,8 @@
       </c>
       <c r="H9" s="4"/>
       <c r="J9" s="3" t="str">
-        <f t="shared" ref="J9" si="3">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A9&amp;"','"&amp;B9&amp;"','"&amp;C9&amp;"','"&amp;D9&amp;"','"&amp;E9&amp;"','"&amp;F9&amp;"','"&amp;G9&amp;"','"&amp;H9&amp;"');"</f>
-        <v>INSERT INTO MENU VALUES('MENU_0007','0','결재 조회','MENU_0005','intrAprvInqy2010.do','Y','7','');</v>
+        <f t="shared" si="1"/>
+        <v>INSERT INTO MENU VALUES('MENU_0007','0','기안 작성','MENU_0006','intrAprvInqy1010.do','Y','7','');</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1869,13 +1919,13 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>260</v>
+        <v>47</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>42</v>
@@ -1885,8 +1935,8 @@
       </c>
       <c r="H10" s="4"/>
       <c r="J10" s="3" t="str">
-        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A10&amp;"','"&amp;B10&amp;"','"&amp;C10&amp;"','"&amp;D10&amp;"','"&amp;E10&amp;"','"&amp;F10&amp;"','"&amp;G10&amp;"','"&amp;H10&amp;"');"</f>
-        <v>INSERT INTO MENU VALUES('MENU_0008','0','결재선 관리','MENU_0005','intrAprvInqy4010.do','Y','8','');</v>
+        <f t="shared" ref="J10" si="3">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A10&amp;"','"&amp;B10&amp;"','"&amp;C10&amp;"','"&amp;D10&amp;"','"&amp;E10&amp;"','"&amp;F10&amp;"','"&amp;G10&amp;"','"&amp;H10&amp;"');"</f>
+        <v>INSERT INTO MENU VALUES('MENU_0008','0','결재 조회','MENU_0006','intrAprvInqy2010.do','Y','8','');</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1897,10 +1947,14 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+        <v>214</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>258</v>
+      </c>
       <c r="F11" s="4" t="s">
         <v>42</v>
       </c>
@@ -1909,8 +1963,8 @@
       </c>
       <c r="H11" s="4"/>
       <c r="J11" s="3" t="str">
-        <f t="shared" ref="J11:J12" si="4">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A11&amp;"','"&amp;B11&amp;"','"&amp;C11&amp;"','"&amp;D11&amp;"','"&amp;E11&amp;"','"&amp;F11&amp;"','"&amp;G11&amp;"','"&amp;H11&amp;"');"</f>
-        <v>INSERT INTO MENU VALUES('MENU_0009','0','업무 관리','','','Y','9','');</v>
+        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A11&amp;"','"&amp;B11&amp;"','"&amp;C11&amp;"','"&amp;D11&amp;"','"&amp;E11&amp;"','"&amp;F11&amp;"','"&amp;G11&amp;"','"&amp;H11&amp;"');"</f>
+        <v>INSERT INTO MENU VALUES('MENU_0009','0','결재선 관리','MENU_0006','intrAprvInqy4010.do','Y','9','');</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -1921,14 +1975,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
       <c r="F12" s="4" t="s">
         <v>42</v>
       </c>
@@ -1937,8 +1987,8 @@
       </c>
       <c r="H12" s="4"/>
       <c r="J12" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>INSERT INTO MENU VALUES('MENU_0010','0','업무일지 작성','MENU_0009','intrTaskInqy1010.do','Y','10','');</v>
+        <f t="shared" ref="J12:J13" si="4">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A12&amp;"','"&amp;B12&amp;"','"&amp;C12&amp;"','"&amp;D12&amp;"','"&amp;E12&amp;"','"&amp;F12&amp;"','"&amp;G12&amp;"','"&amp;H12&amp;"');"</f>
+        <v>INSERT INTO MENU VALUES('MENU_0010','0','업무 관리','','','Y','10','');</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -1949,13 +1999,13 @@
         <v>0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>245</v>
+        <v>152</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>242</v>
+        <v>48</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>42</v>
@@ -1965,8 +2015,8 @@
       </c>
       <c r="H13" s="4"/>
       <c r="J13" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0011','0','업무 캘린더','MENU_0009','intrTaskInqy3010.do','Y','11','');</v>
+        <f t="shared" si="4"/>
+        <v>INSERT INTO MENU VALUES('MENU_0011','0','업무일지 작성','MENU_0010','intrTaskInqy1010.do','Y','11','');</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -1977,10 +2027,14 @@
         <v>0</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+        <v>244</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>241</v>
+      </c>
       <c r="F14" s="4" t="s">
         <v>42</v>
       </c>
@@ -1990,7 +2044,7 @@
       <c r="H14" s="4"/>
       <c r="J14" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0012','0','인사정보','','','Y','12','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0012','0','업무 캘린더','MENU_0010','intrTaskInqy3010.do','Y','12','');</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -2001,14 +2055,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>50</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
       <c r="F15" s="4" t="s">
         <v>42</v>
       </c>
@@ -2017,8 +2067,8 @@
       </c>
       <c r="H15" s="4"/>
       <c r="J15" s="3" t="str">
-        <f t="shared" ref="J15" si="5">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A15&amp;"','"&amp;B15&amp;"','"&amp;C15&amp;"','"&amp;D15&amp;"','"&amp;E15&amp;"','"&amp;F15&amp;"','"&amp;G15&amp;"','"&amp;H15&amp;"');"</f>
-        <v>INSERT INTO MENU VALUES('MENU_0013','0','사원 조회','MENU_0012','intrEmpInqy2010.do','Y','13','');</v>
+        <f t="shared" si="1"/>
+        <v>INSERT INTO MENU VALUES('MENU_0013','0','인사정보','','','Y','13','');</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -2029,13 +2079,13 @@
         <v>0</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>217</v>
+        <v>50</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>42</v>
@@ -2045,8 +2095,8 @@
       </c>
       <c r="H16" s="4"/>
       <c r="J16" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0014','0','담당업무 조회','MENU_0012','intrEmpInqy3010.do','Y','14','');</v>
+        <f t="shared" ref="J16:J17" si="5">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A16&amp;"','"&amp;B16&amp;"','"&amp;C16&amp;"','"&amp;D16&amp;"','"&amp;E16&amp;"','"&amp;F16&amp;"','"&amp;G16&amp;"','"&amp;H16&amp;"');"</f>
+        <v>INSERT INTO MENU VALUES('MENU_0014','0','사원 조회','MENU_0013','intrEmpInqy2010.do','Y','14','');</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -2054,13 +2104,17 @@
         <v>28</v>
       </c>
       <c r="B17" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+        <v>215</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>216</v>
+      </c>
       <c r="F17" s="4" t="s">
         <v>42</v>
       </c>
@@ -2069,8 +2123,8 @@
       </c>
       <c r="H17" s="4"/>
       <c r="J17" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0015','1','공유정보 관리','','','Y','15','');</v>
+        <f t="shared" si="5"/>
+        <v>INSERT INTO MENU VALUES('MENU_0015','0','담당업무 조회','MENU_0013','intrEmpInqy3010.do','Y','15','');</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -2081,14 +2135,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>31</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
       <c r="F18" s="4" t="s">
         <v>42</v>
       </c>
@@ -2097,8 +2147,8 @@
       </c>
       <c r="H18" s="4"/>
       <c r="J18" s="3" t="str">
-        <f t="shared" ref="J18" si="6">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A18&amp;"','"&amp;B18&amp;"','"&amp;C18&amp;"','"&amp;D18&amp;"','"&amp;E18&amp;"','"&amp;F18&amp;"','"&amp;G18&amp;"','"&amp;H18&amp;"');"</f>
-        <v>INSERT INTO MENU VALUES('MENU_0016','1','공지사항 관리','MENU_0015','intrBoardInqy1010.do','Y','16','');</v>
+        <f t="shared" si="1"/>
+        <v>INSERT INTO MENU VALUES('MENU_0016','1','공유정보 관리','','','Y','16','');</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -2109,13 +2159,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>209</v>
+        <v>51</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>212</v>
+        <v>31</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>42</v>
@@ -2125,8 +2175,8 @@
       </c>
       <c r="H19" s="4"/>
       <c r="J19" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0017','1','배너 관리','MENU_0015','intrBanrInqy1010.do','Y','17','');</v>
+        <f t="shared" ref="J19" si="6">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A19&amp;"','"&amp;B19&amp;"','"&amp;C19&amp;"','"&amp;D19&amp;"','"&amp;E19&amp;"','"&amp;F19&amp;"','"&amp;G19&amp;"','"&amp;H19&amp;"');"</f>
+        <v>INSERT INTO MENU VALUES('MENU_0017','1','공지사항 관리','MENU_0016','intrBoardInqy1010.do','Y','17','');</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -2137,13 +2187,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>52</v>
+        <v>208</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>53</v>
+        <v>211</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>42</v>
@@ -2153,8 +2203,8 @@
       </c>
       <c r="H20" s="4"/>
       <c r="J20" s="3" t="str">
-        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A20&amp;"','"&amp;B20&amp;"','"&amp;C20&amp;"','"&amp;D20&amp;"','"&amp;E20&amp;"','"&amp;F20&amp;"','"&amp;G20&amp;"','"&amp;H20&amp;"');"</f>
-        <v>INSERT INTO MENU VALUES('MENU_0018','1','업무일지 조회','MENU_0015','intrTaskInqy2010.do','Y','18','');</v>
+        <f t="shared" si="1"/>
+        <v>INSERT INTO MENU VALUES('MENU_0018','1','배너 관리','MENU_0016','intrBanrInqy1010.do','Y','18','');</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -2165,10 +2215,14 @@
         <v>1</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
+        <v>52</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="F21" s="4" t="s">
         <v>42</v>
       </c>
@@ -2177,8 +2231,8 @@
       </c>
       <c r="H21" s="4"/>
       <c r="J21" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0019','1','전자결재 관리','','','Y','19','');</v>
+        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A21&amp;"','"&amp;B21&amp;"','"&amp;C21&amp;"','"&amp;D21&amp;"','"&amp;E21&amp;"','"&amp;F21&amp;"','"&amp;G21&amp;"','"&amp;H21&amp;"');"</f>
+        <v>INSERT INTO MENU VALUES('MENU_0019','1','업무일지 조회','MENU_0016','intrTaskInqy2010.do','Y','19','');</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -2189,14 +2243,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>54</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
       <c r="F22" s="4" t="s">
         <v>42</v>
       </c>
@@ -2206,7 +2256,7 @@
       <c r="H22" s="4"/>
       <c r="J22" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0020','1','양식 관리','MENU_0019','intrTempInqy1010.do','Y','20','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0020','1','전자결재 관리','','','Y','20','');</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
@@ -2217,13 +2267,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>151</v>
+        <v>277</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>42</v>
@@ -2234,7 +2284,7 @@
       <c r="H23" s="4"/>
       <c r="J23" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0021','1','프로젝트 관리','MENU_0019','intrProjInqy1010.do','Y','21','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0021','1','결재양식 관리','MENU_0020','intrTempInqy1010.do','Y','21','');</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
@@ -2245,10 +2295,14 @@
         <v>1</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+        <v>278</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>272</v>
+      </c>
       <c r="F24" s="4" t="s">
         <v>42</v>
       </c>
@@ -2257,8 +2311,8 @@
       </c>
       <c r="H24" s="4"/>
       <c r="J24" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0022','1','인사정보','','','Y','22','');</v>
+        <f t="shared" ref="J24" si="7">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A24&amp;"','"&amp;B24&amp;"','"&amp;C24&amp;"','"&amp;D24&amp;"','"&amp;E24&amp;"','"&amp;F24&amp;"','"&amp;G24&amp;"','"&amp;H24&amp;"');"</f>
+        <v>INSERT INTO MENU VALUES('MENU_0022','1','결재양식 연동','MENU_0020','intrTempInqy2010.do','Y','22','');</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -2269,13 +2323,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>42</v>
@@ -2286,25 +2340,21 @@
       <c r="H25" s="4"/>
       <c r="J25" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0023','1','사원 관리','MENU_0022','intrEmpInqy1010.do','Y','23','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0023','1','프로젝트 관리','MENU_0020','intrProjInqy1010.do','Y','23','');</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B26" s="4">
         <v>1</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>218</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
       <c r="F26" s="4" t="s">
         <v>42</v>
       </c>
@@ -2313,22 +2363,26 @@
       </c>
       <c r="H26" s="4"/>
       <c r="J26" s="3" t="str">
-        <f t="shared" ref="J26" si="7">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A26&amp;"','"&amp;B26&amp;"','"&amp;C26&amp;"','"&amp;D26&amp;"','"&amp;E26&amp;"','"&amp;F26&amp;"','"&amp;G26&amp;"','"&amp;H26&amp;"');"</f>
-        <v>INSERT INTO MENU VALUES('MENU_0024','1','인사 통계','MENU_0022','intrEmpInqy4010.do','Y','24','');</v>
+        <f t="shared" si="1"/>
+        <v>INSERT INTO MENU VALUES('MENU_0024','1','인사정보','','','Y','24','');</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B27" s="4">
         <v>1</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+        <v>55</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="F27" s="4" t="s">
         <v>42</v>
       </c>
@@ -2338,24 +2392,24 @@
       <c r="H27" s="4"/>
       <c r="J27" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0025','1','시스템 관리','','','Y','25','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0025','1','사원 관리','MENU_0024','intrEmpInqy1010.do','Y','25','');</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B28" s="4">
         <v>1</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>58</v>
+        <v>222</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>210</v>
+        <v>151</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>59</v>
+        <v>217</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>42</v>
@@ -2365,26 +2419,22 @@
       </c>
       <c r="H28" s="4"/>
       <c r="J28" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0026','1','권한 관리','MENU_0025','intrAuthInqy1010.do','Y','26','');</v>
+        <f t="shared" ref="J28" si="8">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A28&amp;"','"&amp;B28&amp;"','"&amp;C28&amp;"','"&amp;D28&amp;"','"&amp;E28&amp;"','"&amp;F28&amp;"','"&amp;G28&amp;"','"&amp;H28&amp;"');"</f>
+        <v>INSERT INTO MENU VALUES('MENU_0026','1','인사 통계','MENU_0024','intrEmpInqy4010.do','Y','26','');</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B29" s="4">
         <v>1</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>61</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
       <c r="F29" s="4" t="s">
         <v>42</v>
       </c>
@@ -2394,24 +2444,24 @@
       <c r="H29" s="4"/>
       <c r="J29" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0027','1','메뉴 권한 부여','MENU_0025','intrAuthInqy2010.do','Y','27','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0027','1','시스템 관리','','','Y','27','');</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B30" s="4">
         <v>1</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>42</v>
@@ -2421,25 +2471,25 @@
       </c>
       <c r="H30" s="4"/>
       <c r="J30" s="3" t="str">
-        <f t="shared" ref="J30" si="8">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A30&amp;"','"&amp;B30&amp;"','"&amp;C30&amp;"','"&amp;D30&amp;"','"&amp;E30&amp;"','"&amp;F30&amp;"','"&amp;G30&amp;"','"&amp;H30&amp;"');"</f>
-        <v>INSERT INTO MENU VALUES('MENU_0028','1','사용자 권한 부여','MENU_0025','intrAuthInqy3010.do','Y','28','');</v>
+        <f t="shared" si="1"/>
+        <v>INSERT INTO MENU VALUES('MENU_0028','1','권한 관리','MENU_0027','intrAuthInqy1010.do','Y','28','');</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B31" s="4">
         <v>1</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>42</v>
@@ -2450,7 +2500,63 @@
       <c r="H31" s="4"/>
       <c r="J31" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0029','1','쿼리 입력','MENU_0025','intrQueryInqy1010.do','Y','29','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0029','1','메뉴 권한 부여','MENU_0027','intrAuthInqy2010.do','Y','29','');</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B32" s="4">
+        <v>1</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G32" s="4">
+        <v>30</v>
+      </c>
+      <c r="H32" s="4"/>
+      <c r="J32" s="3" t="str">
+        <f t="shared" ref="J32" si="9">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A32&amp;"','"&amp;B32&amp;"','"&amp;C32&amp;"','"&amp;D32&amp;"','"&amp;E32&amp;"','"&amp;F32&amp;"','"&amp;G32&amp;"','"&amp;H32&amp;"');"</f>
+        <v>INSERT INTO MENU VALUES('MENU_0030','1','사용자 권한 부여','MENU_0027','intrAuthInqy3010.do','Y','30','');</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B33" s="4">
+        <v>1</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G33" s="4">
+        <v>31</v>
+      </c>
+      <c r="H33" s="4"/>
+      <c r="J33" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>INSERT INTO MENU VALUES('MENU_0031','1','쿼리 입력','MENU_0027','intrQueryInqy1010.do','Y','31','');</v>
       </c>
     </row>
   </sheetData>
@@ -2465,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06E19CE9-CDB6-46E2-AE0E-C80BE1FBF213}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="8" width="17.625" style="2" customWidth="1"/>
@@ -2512,13 +2618,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D3" s="4">
         <v>20250520</v>
@@ -2540,13 +2646,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>265</v>
-      </c>
       <c r="C4" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D4" s="4">
         <v>20250520</v>
@@ -2568,13 +2674,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>146</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D5" s="4">
         <v>20250520</v>
@@ -2596,13 +2702,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>147</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D6" s="4">
         <v>20250520</v>
@@ -2624,13 +2730,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D7" s="4">
         <v>20250520</v>
@@ -2652,13 +2758,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D8" s="4">
         <v>20250520</v>
@@ -2680,13 +2786,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D9" s="4">
         <v>20250520</v>
@@ -2708,13 +2814,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D10" s="4">
         <v>20250520</v>
@@ -2736,13 +2842,13 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D11" s="4">
         <v>20250520</v>
@@ -2764,13 +2870,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D12" s="4">
         <v>20250520</v>
@@ -2792,13 +2898,13 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D13" s="4">
         <v>20250520</v>
@@ -2820,13 +2926,13 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D14" s="4">
         <v>20250520</v>
@@ -2848,13 +2954,13 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D15" s="4">
         <v>20250520</v>
@@ -2876,13 +2982,13 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D16" s="4">
         <v>20250520</v>
@@ -2904,13 +3010,13 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D17" s="4">
         <v>20250520</v>
@@ -2932,13 +3038,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D18" s="4">
         <v>20250520</v>
@@ -2960,13 +3066,13 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D19" s="4">
         <v>20250520</v>
@@ -2988,13 +3094,13 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D20" s="4">
         <v>20250520</v>
@@ -3016,13 +3122,13 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D21" s="4">
         <v>20250520</v>
@@ -3044,13 +3150,13 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D22" s="4">
         <v>20250520</v>
@@ -3072,13 +3178,13 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D23" s="4">
         <v>20250520</v>
@@ -3100,13 +3206,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>206</v>
-      </c>
       <c r="C24" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D24" s="4">
         <v>20250520</v>
@@ -3128,13 +3234,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D25" s="4">
         <v>20250520</v>
@@ -3156,13 +3262,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D26" s="4">
         <v>20250520</v>
@@ -3184,13 +3290,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D27" s="4">
         <v>20250520</v>
@@ -3206,8 +3312,92 @@
       </c>
       <c r="H27" s="4"/>
       <c r="J27" s="3" t="str">
-        <f t="shared" ref="J27" si="3">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A27&amp;"','"&amp;B27&amp;"','"&amp;C27&amp;"','"&amp;D27&amp;"','"&amp;E27&amp;"','"&amp;F27&amp;"','"&amp;G27&amp;"','"&amp;H27&amp;"');"</f>
+        <f t="shared" ref="J27:J29" si="3">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A27&amp;"','"&amp;B27&amp;"','"&amp;C27&amp;"','"&amp;D27&amp;"','"&amp;E27&amp;"','"&amp;F27&amp;"','"&amp;G27&amp;"','"&amp;H27&amp;"');"</f>
         <v>INSERT INTO COMMCODE VALUES('RSLT_0030','취소','RSLT','20250520','80525','Y','3','');</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D28" s="4">
+        <v>20250520</v>
+      </c>
+      <c r="E28" s="4">
+        <v>80525</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G28" s="4">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4"/>
+      <c r="J28" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO COMMCODE VALUES('LOC_0010','회의실 (대)','LOC','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D29" s="4">
+        <v>20250520</v>
+      </c>
+      <c r="E29" s="4">
+        <v>80525</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G29" s="4">
+        <v>2</v>
+      </c>
+      <c r="H29" s="4"/>
+      <c r="J29" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>INSERT INTO COMMCODE VALUES('LOC_0020','회의실 (중)','LOC','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D30" s="4">
+        <v>20250520</v>
+      </c>
+      <c r="E30" s="4">
+        <v>80525</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" s="4">
+        <v>3</v>
+      </c>
+      <c r="H30" s="4"/>
+      <c r="J30" s="3" t="str">
+        <f t="shared" ref="J30" si="4">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A30&amp;"','"&amp;B30&amp;"','"&amp;C30&amp;"','"&amp;D30&amp;"','"&amp;E30&amp;"','"&amp;F30&amp;"','"&amp;G30&amp;"','"&amp;H30&amp;"');"</f>
+        <v>INSERT INTO COMMCODE VALUES('LOC_0030','회의실 (소)','LOC','20250520','80525','Y','3','');</v>
       </c>
     </row>
   </sheetData>
@@ -3304,7 +3494,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DBD6899-63FF-4260-80D6-0650038B0C85}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="15.625" style="2" customWidth="1"/>
@@ -3779,7 +3969,7 @@
         <v>34</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>14</v>
@@ -3798,7 +3988,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>14</v>
@@ -3817,7 +4007,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>14</v>
@@ -3836,7 +4026,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -3855,7 +4045,7 @@
         <v>34</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>14</v>
@@ -3874,7 +4064,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>14</v>
@@ -3886,6 +4076,44 @@
       <c r="G31" s="3" t="str">
         <f t="shared" si="3"/>
         <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0029','Y','29','');</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="4">
+        <v>30</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="G32" s="3" t="str">
+        <f t="shared" ref="G32:G33" si="4">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A32&amp;"','"&amp;B32&amp;"','"&amp;C32&amp;"','"&amp;D32&amp;"','"&amp;E32&amp;"');"</f>
+        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0030','Y','30','');</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="4">
+        <v>31</v>
+      </c>
+      <c r="E33" s="4"/>
+      <c r="G33" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0031','Y','31','');</v>
       </c>
     </row>
   </sheetData>
@@ -3937,7 +4165,7 @@
         <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>42</v>
@@ -4793,7 +5021,7 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -4804,16 +5032,16 @@
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>6</v>
@@ -4827,13 +5055,13 @@
     </row>
     <row r="3" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D3" s="4">
         <v>20250520</v>
@@ -4902,13 +5130,13 @@
     </row>
     <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D4" s="4">
         <v>20250520</v>
@@ -4979,13 +5207,13 @@
     </row>
     <row r="5" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D5" s="4">
         <v>20250520</v>
@@ -5056,13 +5284,13 @@
     </row>
     <row r="6" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D6" s="4">
         <v>20250520</v>
@@ -5154,7 +5382,7 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -5173,31 +5401,31 @@
     </row>
     <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>0</v>
@@ -5220,13 +5448,13 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>257</v>
-      </c>
       <c r="C3" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D3" s="4">
         <v>19900101</v>
@@ -5235,7 +5463,7 @@
         <v>19901231</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>85</v>

--- a/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
+++ b/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\knn\Documents\hikr90\02.프로젝트\01.인트라넷\01.설계\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7401C4AA-AFAA-4D59-A504-7E6CF4AC1755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC26A93-0858-494D-A879-3F31C45A918E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="793" xr2:uid="{B204C4DA-9ED1-4F0A-AC7E-C11DE778500E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="793" activeTab="2" xr2:uid="{B204C4DA-9ED1-4F0A-AC7E-C11DE778500E}"/>
   </bookViews>
   <sheets>
     <sheet name="MENU" sheetId="8" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="276">
   <si>
     <t>EMP_IDX</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1224,13 +1224,6 @@
     <t>MENU_0030</t>
   </si>
   <si>
-    <t>intrTempInqy2010.do</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MENU_0031</t>
-  </si>
-  <si>
     <t>내부규정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1244,10 +1237,6 @@
   </si>
   <si>
     <t>결재양식 관리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>결재양식 연동</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1672,7 +1661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60644FAD-9B99-49D5-B453-33EA3359146C}">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="15.625" style="2" customWidth="1"/>
@@ -1799,7 +1788,7 @@
       </c>
       <c r="H5" s="4"/>
       <c r="J5" s="3" t="str">
-        <f t="shared" ref="J5:J33" si="1">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A5&amp;"','"&amp;B5&amp;"','"&amp;C5&amp;"','"&amp;D5&amp;"','"&amp;E5&amp;"','"&amp;F5&amp;"','"&amp;G5&amp;"','"&amp;H5&amp;"');"</f>
+        <f t="shared" ref="J5:J32" si="1">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A5&amp;"','"&amp;B5&amp;"','"&amp;C5&amp;"','"&amp;D5&amp;"','"&amp;E5&amp;"','"&amp;F5&amp;"','"&amp;G5&amp;"','"&amp;H5&amp;"');"</f>
         <v>INSERT INTO MENU VALUES('MENU_0003','0','회의 관리','MENU_0001','intrMtgInqy1010.do','Y','3','');</v>
       </c>
     </row>
@@ -1811,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>40</v>
@@ -1839,13 +1828,13 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>42</v>
@@ -2267,7 +2256,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>38</v>
@@ -2295,24 +2284,24 @@
         <v>1</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>278</v>
+        <v>150</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>38</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>272</v>
+        <v>70</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>42</v>
       </c>
       <c r="G24" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H24" s="4"/>
       <c r="J24" s="3" t="str">
-        <f t="shared" ref="J24" si="7">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A24&amp;"','"&amp;B24&amp;"','"&amp;C24&amp;"','"&amp;D24&amp;"','"&amp;E24&amp;"','"&amp;F24&amp;"','"&amp;G24&amp;"','"&amp;H24&amp;"');"</f>
-        <v>INSERT INTO MENU VALUES('MENU_0022','1','결재양식 연동','MENU_0020','intrTempInqy2010.do','Y','22','');</v>
+        <f t="shared" si="1"/>
+        <v>INSERT INTO MENU VALUES('MENU_0022','1','프로젝트 관리','MENU_0020','intrProjInqy1010.do','Y','23','');</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -2323,24 +2312,20 @@
         <v>1</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>70</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
       <c r="F25" s="4" t="s">
         <v>42</v>
       </c>
       <c r="G25" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" s="4"/>
       <c r="J25" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0023','1','프로젝트 관리','MENU_0020','intrProjInqy1010.do','Y','23','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0023','1','인사정보','','','Y','24','');</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
@@ -2351,20 +2336,24 @@
         <v>1</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+        <v>55</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="F26" s="4" t="s">
         <v>42</v>
       </c>
       <c r="G26" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H26" s="4"/>
       <c r="J26" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0024','1','인사정보','','','Y','24','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0024','1','사원 관리','MENU_0024','intrEmpInqy1010.do','Y','25','');</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
@@ -2375,24 +2364,24 @@
         <v>1</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>55</v>
+        <v>222</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>151</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>56</v>
+        <v>217</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>42</v>
       </c>
       <c r="G27" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H27" s="4"/>
       <c r="J27" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0025','1','사원 관리','MENU_0024','intrEmpInqy1010.do','Y','25','');</v>
+        <f t="shared" ref="J27" si="7">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A27&amp;"','"&amp;B27&amp;"','"&amp;C27&amp;"','"&amp;D27&amp;"','"&amp;E27&amp;"','"&amp;F27&amp;"','"&amp;G27&amp;"','"&amp;H27&amp;"');"</f>
+        <v>INSERT INTO MENU VALUES('MENU_0025','1','인사 통계','MENU_0024','intrEmpInqy4010.do','Y','26','');</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
@@ -2403,24 +2392,20 @@
         <v>1</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>217</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
       <c r="F28" s="4" t="s">
         <v>42</v>
       </c>
       <c r="G28" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H28" s="4"/>
       <c r="J28" s="3" t="str">
-        <f t="shared" ref="J28" si="8">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A28&amp;"','"&amp;B28&amp;"','"&amp;C28&amp;"','"&amp;D28&amp;"','"&amp;E28&amp;"','"&amp;F28&amp;"','"&amp;G28&amp;"','"&amp;H28&amp;"');"</f>
-        <v>INSERT INTO MENU VALUES('MENU_0026','1','인사 통계','MENU_0024','intrEmpInqy4010.do','Y','26','');</v>
+        <f t="shared" si="1"/>
+        <v>INSERT INTO MENU VALUES('MENU_0026','1','시스템 관리','','','Y','27','');</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
@@ -2431,20 +2416,24 @@
         <v>1</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
+        <v>58</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="F29" s="4" t="s">
         <v>42</v>
       </c>
       <c r="G29" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H29" s="4"/>
       <c r="J29" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0027','1','시스템 관리','','','Y','27','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0027','1','권한 관리','MENU_0027','intrAuthInqy1010.do','Y','28','');</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -2455,24 +2444,24 @@
         <v>1</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>213</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>42</v>
       </c>
       <c r="G30" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H30" s="4"/>
       <c r="J30" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0028','1','권한 관리','MENU_0027','intrAuthInqy1010.do','Y','28','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0028','1','메뉴 권한 부여','MENU_0027','intrAuthInqy2010.do','Y','29','');</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
@@ -2483,24 +2472,24 @@
         <v>1</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>213</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>42</v>
       </c>
       <c r="G31" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H31" s="4"/>
       <c r="J31" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0029','1','메뉴 권한 부여','MENU_0027','intrAuthInqy2010.do','Y','29','');</v>
+        <f t="shared" ref="J31" si="8">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A31&amp;"','"&amp;B31&amp;"','"&amp;C31&amp;"','"&amp;D31&amp;"','"&amp;E31&amp;"','"&amp;F31&amp;"','"&amp;G31&amp;"','"&amp;H31&amp;"');"</f>
+        <v>INSERT INTO MENU VALUES('MENU_0029','1','사용자 권한 부여','MENU_0027','intrAuthInqy3010.do','Y','30','');</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
@@ -2511,52 +2500,24 @@
         <v>1</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>213</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>42</v>
       </c>
       <c r="G32" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H32" s="4"/>
       <c r="J32" s="3" t="str">
-        <f t="shared" ref="J32" si="9">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A32&amp;"','"&amp;B32&amp;"','"&amp;C32&amp;"','"&amp;D32&amp;"','"&amp;E32&amp;"','"&amp;F32&amp;"','"&amp;G32&amp;"','"&amp;H32&amp;"');"</f>
-        <v>INSERT INTO MENU VALUES('MENU_0030','1','사용자 권한 부여','MENU_0027','intrAuthInqy3010.do','Y','30','');</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="B33" s="4">
-        <v>1</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G33" s="4">
-        <v>31</v>
-      </c>
-      <c r="H33" s="4"/>
-      <c r="J33" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0031','1','쿼리 입력','MENU_0027','intrQueryInqy1010.do','Y','31','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0030','1','쿼리 입력','MENU_0027','intrQueryInqy1010.do','Y','31','');</v>
       </c>
     </row>
   </sheetData>
@@ -3494,7 +3455,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DBD6899-63FF-4260-80D6-0650038B0C85}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="15.625" style="2" customWidth="1"/>
@@ -4093,27 +4054,8 @@
       </c>
       <c r="E32" s="4"/>
       <c r="G32" s="3" t="str">
-        <f t="shared" ref="G32:G33" si="4">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A32&amp;"','"&amp;B32&amp;"','"&amp;C32&amp;"','"&amp;D32&amp;"','"&amp;E32&amp;"');"</f>
+        <f t="shared" ref="G32" si="4">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A32&amp;"','"&amp;B32&amp;"','"&amp;C32&amp;"','"&amp;D32&amp;"','"&amp;E32&amp;"');"</f>
         <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0030','Y','30','');</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" s="4">
-        <v>31</v>
-      </c>
-      <c r="E33" s="4"/>
-      <c r="G33" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0031','Y','31','');</v>
       </c>
     </row>
   </sheetData>

--- a/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
+++ b/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\knn\Documents\hikr90\02.프로젝트\01.인트라넷\01.설계\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC26A93-0858-494D-A879-3F31C45A918E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C0B9A8-222A-41E1-9361-957811B1F88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="793" activeTab="2" xr2:uid="{B204C4DA-9ED1-4F0A-AC7E-C11DE778500E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="793" xr2:uid="{B204C4DA-9ED1-4F0A-AC7E-C11DE778500E}"/>
   </bookViews>
   <sheets>
     <sheet name="MENU" sheetId="8" r:id="rId1"/>
@@ -2339,7 +2339,7 @@
         <v>55</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>56</v>
@@ -2353,7 +2353,7 @@
       <c r="H26" s="4"/>
       <c r="J26" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0024','1','사원 관리','MENU_0024','intrEmpInqy1010.do','Y','25','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0024','1','사원 관리','MENU_0023','intrEmpInqy1010.do','Y','25','');</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
@@ -2367,7 +2367,7 @@
         <v>222</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>217</v>
@@ -2381,7 +2381,7 @@
       <c r="H27" s="4"/>
       <c r="J27" s="3" t="str">
         <f t="shared" ref="J27" si="7">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A27&amp;"','"&amp;B27&amp;"','"&amp;C27&amp;"','"&amp;D27&amp;"','"&amp;E27&amp;"','"&amp;F27&amp;"','"&amp;G27&amp;"','"&amp;H27&amp;"');"</f>
-        <v>INSERT INTO MENU VALUES('MENU_0025','1','인사 통계','MENU_0024','intrEmpInqy4010.do','Y','26','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0025','1','인사 통계','MENU_0023','intrEmpInqy4010.do','Y','26','');</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
@@ -2419,7 +2419,7 @@
         <v>58</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>59</v>
@@ -2433,7 +2433,7 @@
       <c r="H29" s="4"/>
       <c r="J29" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0027','1','권한 관리','MENU_0027','intrAuthInqy1010.do','Y','28','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0027','1','권한 관리','MENU_0026','intrAuthInqy1010.do','Y','28','');</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -2447,7 +2447,7 @@
         <v>60</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>61</v>
@@ -2461,7 +2461,7 @@
       <c r="H30" s="4"/>
       <c r="J30" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0028','1','메뉴 권한 부여','MENU_0027','intrAuthInqy2010.do','Y','29','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0028','1','메뉴 권한 부여','MENU_0026','intrAuthInqy2010.do','Y','29','');</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
@@ -2475,7 +2475,7 @@
         <v>62</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>63</v>
@@ -2489,7 +2489,7 @@
       <c r="H31" s="4"/>
       <c r="J31" s="3" t="str">
         <f t="shared" ref="J31" si="8">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A31&amp;"','"&amp;B31&amp;"','"&amp;C31&amp;"','"&amp;D31&amp;"','"&amp;E31&amp;"','"&amp;F31&amp;"','"&amp;G31&amp;"','"&amp;H31&amp;"');"</f>
-        <v>INSERT INTO MENU VALUES('MENU_0029','1','사용자 권한 부여','MENU_0027','intrAuthInqy3010.do','Y','30','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0029','1','사용자 권한 부여','MENU_0026','intrAuthInqy3010.do','Y','30','');</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
@@ -2503,7 +2503,7 @@
         <v>65</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>66</v>
@@ -2517,7 +2517,7 @@
       <c r="H32" s="4"/>
       <c r="J32" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0030','1','쿼리 입력','MENU_0027','intrQueryInqy1010.do','Y','31','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0030','1','쿼리 입력','MENU_0026','intrQueryInqy1010.do','Y','31','');</v>
       </c>
     </row>
   </sheetData>

--- a/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
+++ b/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\knn\Documents\hikr90\02.프로젝트\01.인트라넷\01.설계\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C0B9A8-222A-41E1-9361-957811B1F88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3306B86-95C3-4B2A-96F8-F22920459A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="793" xr2:uid="{B204C4DA-9ED1-4F0A-AC7E-C11DE778500E}"/>
   </bookViews>

--- a/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
+++ b/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\knn\Documents\hikr90\02.프로젝트\01.인트라넷\01.설계\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3306B86-95C3-4B2A-96F8-F22920459A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B3395A-18C3-4DA2-9392-8732BFA29734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="793" xr2:uid="{B204C4DA-9ED1-4F0A-AC7E-C11DE778500E}"/>
   </bookViews>
   <sheets>
     <sheet name="MENU" sheetId="8" r:id="rId1"/>
-    <sheet name="AUTH" sheetId="20" r:id="rId2"/>
-    <sheet name="MENU_AUTH" sheetId="21" r:id="rId3"/>
-    <sheet name="EMP_AUTH" sheetId="24" r:id="rId4"/>
+    <sheet name="ROLE" sheetId="20" r:id="rId2"/>
+    <sheet name="MENU_ROLE" sheetId="21" r:id="rId3"/>
+    <sheet name="EMP_ROLE" sheetId="24" r:id="rId4"/>
     <sheet name="EMPINFO" sheetId="22" r:id="rId5"/>
     <sheet name="ORG" sheetId="25" r:id="rId6"/>
     <sheet name="RANK" sheetId="26" r:id="rId7"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="278">
   <si>
     <t>EMP_IDX</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -147,18 +147,6 @@
     <t>intrBoardInqy1010.do</t>
   </si>
   <si>
-    <t>AUTH_CD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AUTH_NM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AUTH_0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>관리자 권한</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -232,21 +220,12 @@
     <t>권한 관리</t>
   </si>
   <si>
-    <t>intrAuthInqy1010.do</t>
-  </si>
-  <si>
     <t>메뉴 권한 부여</t>
   </si>
   <si>
-    <t>intrAuthInqy2010.do</t>
-  </si>
-  <si>
     <t>사용자 권한 부여</t>
   </si>
   <si>
-    <t>intrAuthInqy3010.do</t>
-  </si>
-  <si>
     <t>MENU_0022</t>
   </si>
   <si>
@@ -263,26 +242,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AUTH</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>intrProjInqy1010.do</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AUTH_0002</t>
-  </si>
-  <si>
     <t>테스트 권한</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MENU_AUTH</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EMP_AUTH</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1238,6 +1202,45 @@
   <si>
     <t>결재양식 관리</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROLE_CD</t>
+  </si>
+  <si>
+    <t>ROLE_CD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROLE_0001</t>
+  </si>
+  <si>
+    <t>ROLE_0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROLE_NM</t>
+  </si>
+  <si>
+    <t>ROLE_0002</t>
+  </si>
+  <si>
+    <t>EMP_ROLE</t>
+  </si>
+  <si>
+    <t>MENU_ROLE</t>
+  </si>
+  <si>
+    <t>intrRoleInqy1010.do</t>
+  </si>
+  <si>
+    <t>intrRoleInqy2010.do</t>
+  </si>
+  <si>
+    <t>intrRoleInqy3010.do</t>
   </si>
 </sst>
 </file>
@@ -1676,7 +1679,7 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -1714,18 +1717,18 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4">
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G3" s="4">
         <v>1</v>
@@ -1744,16 +1747,16 @@
         <v>0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G4" s="4">
         <v>2</v>
@@ -1772,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G5" s="4">
         <v>3</v>
@@ -1800,16 +1803,16 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G6" s="4">
         <v>4</v>
@@ -1828,16 +1831,16 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G7" s="4">
         <v>5</v>
@@ -1856,12 +1859,12 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G8" s="4">
         <v>6</v>
@@ -1880,16 +1883,16 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G9" s="4">
         <v>7</v>
@@ -1908,16 +1911,16 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G10" s="4">
         <v>8</v>
@@ -1936,16 +1939,16 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G11" s="4">
         <v>9</v>
@@ -1964,12 +1967,12 @@
         <v>0</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G12" s="4">
         <v>10</v>
@@ -1988,16 +1991,16 @@
         <v>0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G13" s="4">
         <v>11</v>
@@ -2016,16 +2019,16 @@
         <v>0</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G14" s="4">
         <v>12</v>
@@ -2044,12 +2047,12 @@
         <v>0</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G15" s="4">
         <v>13</v>
@@ -2068,16 +2071,16 @@
         <v>0</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G16" s="4">
         <v>14</v>
@@ -2096,16 +2099,16 @@
         <v>0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G17" s="4">
         <v>15</v>
@@ -2124,12 +2127,12 @@
         <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G18" s="4">
         <v>16</v>
@@ -2148,7 +2151,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>29</v>
@@ -2157,7 +2160,7 @@
         <v>31</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G19" s="4">
         <v>17</v>
@@ -2170,22 +2173,22 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G20" s="4">
         <v>18</v>
@@ -2198,22 +2201,22 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B21" s="4">
         <v>1</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G21" s="4">
         <v>19</v>
@@ -2226,18 +2229,18 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B22" s="4">
         <v>1</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G22" s="4">
         <v>20</v>
@@ -2250,22 +2253,22 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B23" s="4">
         <v>1</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G23" s="4">
         <v>21</v>
@@ -2278,22 +2281,22 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B24" s="4">
         <v>1</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G24" s="4">
         <v>23</v>
@@ -2306,18 +2309,18 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G25" s="4">
         <v>24</v>
@@ -2330,22 +2333,22 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="B26" s="4">
         <v>1</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G26" s="4">
         <v>25</v>
@@ -2358,22 +2361,22 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B27" s="4">
         <v>1</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G27" s="4">
         <v>26</v>
@@ -2386,18 +2389,18 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B28" s="4">
         <v>1</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G28" s="4">
         <v>27</v>
@@ -2410,22 +2413,22 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B29" s="4">
         <v>1</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>59</v>
+        <v>275</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G29" s="4">
         <v>28</v>
@@ -2433,27 +2436,27 @@
       <c r="H29" s="4"/>
       <c r="J29" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0027','1','권한 관리','MENU_0026','intrAuthInqy1010.do','Y','28','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0027','1','권한 관리','MENU_0026','intrRoleInqy1010.do','Y','28','');</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="B30" s="4">
         <v>1</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>61</v>
+        <v>276</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G30" s="4">
         <v>29</v>
@@ -2461,27 +2464,27 @@
       <c r="H30" s="4"/>
       <c r="J30" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO MENU VALUES('MENU_0028','1','메뉴 권한 부여','MENU_0026','intrAuthInqy2010.do','Y','29','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0028','1','메뉴 권한 부여','MENU_0026','intrRoleInqy2010.do','Y','29','');</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="B31" s="4">
         <v>1</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>63</v>
+        <v>277</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G31" s="4">
         <v>30</v>
@@ -2489,27 +2492,27 @@
       <c r="H31" s="4"/>
       <c r="J31" s="3" t="str">
         <f t="shared" ref="J31" si="8">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A31&amp;"','"&amp;B31&amp;"','"&amp;C31&amp;"','"&amp;D31&amp;"','"&amp;E31&amp;"','"&amp;F31&amp;"','"&amp;G31&amp;"','"&amp;H31&amp;"');"</f>
-        <v>INSERT INTO MENU VALUES('MENU_0029','1','사용자 권한 부여','MENU_0026','intrAuthInqy3010.do','Y','30','');</v>
+        <v>INSERT INTO MENU VALUES('MENU_0029','1','사용자 권한 부여','MENU_0026','intrRoleInqy3010.do','Y','30','');</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B32" s="4">
         <v>1</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G32" s="4">
         <v>31</v>
@@ -2541,7 +2544,7 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -2553,13 +2556,13 @@
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>4</v>
@@ -2579,13 +2582,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="D3" s="4">
         <v>20250520</v>
@@ -2594,7 +2597,7 @@
         <v>80516</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G3" s="4">
         <v>1</v>
@@ -2607,13 +2610,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="D4" s="4">
         <v>20250520</v>
@@ -2622,7 +2625,7 @@
         <v>80525</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G4" s="4">
         <v>2</v>
@@ -2635,13 +2638,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D5" s="4">
         <v>20250520</v>
@@ -2650,7 +2653,7 @@
         <v>80525</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G5" s="4">
         <v>1</v>
@@ -2663,13 +2666,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D6" s="4">
         <v>20250520</v>
@@ -2678,7 +2681,7 @@
         <v>80525</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G6" s="4">
         <v>2</v>
@@ -2691,13 +2694,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D7" s="4">
         <v>20250520</v>
@@ -2706,7 +2709,7 @@
         <v>80525</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G7" s="4">
         <v>3</v>
@@ -2719,13 +2722,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D8" s="4">
         <v>20250520</v>
@@ -2734,7 +2737,7 @@
         <v>80525</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G8" s="4">
         <v>1</v>
@@ -2747,13 +2750,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D9" s="4">
         <v>20250520</v>
@@ -2762,7 +2765,7 @@
         <v>80525</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G9" s="4">
         <v>2</v>
@@ -2775,13 +2778,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D10" s="4">
         <v>20250520</v>
@@ -2790,7 +2793,7 @@
         <v>80525</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G10" s="4">
         <v>3</v>
@@ -2803,13 +2806,13 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D11" s="4">
         <v>20250520</v>
@@ -2818,7 +2821,7 @@
         <v>80525</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G11" s="4">
         <v>4</v>
@@ -2831,13 +2834,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D12" s="4">
         <v>20250520</v>
@@ -2846,7 +2849,7 @@
         <v>80525</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G12" s="4">
         <v>5</v>
@@ -2859,13 +2862,13 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D13" s="4">
         <v>20250520</v>
@@ -2874,7 +2877,7 @@
         <v>80525</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G13" s="4">
         <v>1</v>
@@ -2887,13 +2890,13 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D14" s="4">
         <v>20250520</v>
@@ -2902,7 +2905,7 @@
         <v>80525</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G14" s="4">
         <v>2</v>
@@ -2915,13 +2918,13 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D15" s="4">
         <v>20250520</v>
@@ -2930,7 +2933,7 @@
         <v>80525</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G15" s="4">
         <v>3</v>
@@ -2943,13 +2946,13 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D16" s="4">
         <v>20250520</v>
@@ -2958,7 +2961,7 @@
         <v>80525</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G16" s="4">
         <v>1</v>
@@ -2971,13 +2974,13 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D17" s="4">
         <v>20250520</v>
@@ -2986,7 +2989,7 @@
         <v>80525</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G17" s="4">
         <v>2</v>
@@ -2999,13 +3002,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D18" s="4">
         <v>20250520</v>
@@ -3014,7 +3017,7 @@
         <v>80525</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G18" s="4">
         <v>3</v>
@@ -3027,13 +3030,13 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D19" s="4">
         <v>20250520</v>
@@ -3042,7 +3045,7 @@
         <v>80525</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G19" s="4">
         <v>1</v>
@@ -3055,13 +3058,13 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D20" s="4">
         <v>20250520</v>
@@ -3070,7 +3073,7 @@
         <v>80525</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G20" s="4">
         <v>2</v>
@@ -3083,13 +3086,13 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D21" s="4">
         <v>20250520</v>
@@ -3098,7 +3101,7 @@
         <v>80525</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G21" s="4">
         <v>1</v>
@@ -3111,13 +3114,13 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D22" s="4">
         <v>20250520</v>
@@ -3126,7 +3129,7 @@
         <v>80525</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G22" s="4">
         <v>2</v>
@@ -3139,13 +3142,13 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>195</v>
       </c>
       <c r="D23" s="4">
         <v>20250520</v>
@@ -3154,7 +3157,7 @@
         <v>80525</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G23" s="4">
         <v>3</v>
@@ -3167,13 +3170,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D24" s="4">
         <v>20250520</v>
@@ -3182,7 +3185,7 @@
         <v>80525</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G24" s="4">
         <v>4</v>
@@ -3195,13 +3198,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D25" s="4">
         <v>20250520</v>
@@ -3210,7 +3213,7 @@
         <v>80525</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G25" s="4">
         <v>1</v>
@@ -3223,13 +3226,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D26" s="4">
         <v>20250520</v>
@@ -3238,7 +3241,7 @@
         <v>80525</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G26" s="4">
         <v>2</v>
@@ -3251,13 +3254,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D27" s="4">
         <v>20250520</v>
@@ -3266,7 +3269,7 @@
         <v>80525</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G27" s="4">
         <v>3</v>
@@ -3279,13 +3282,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D28" s="4">
         <v>20250520</v>
@@ -3294,7 +3297,7 @@
         <v>80525</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G28" s="4">
         <v>1</v>
@@ -3307,13 +3310,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D29" s="4">
         <v>20250520</v>
@@ -3322,7 +3325,7 @@
         <v>80525</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G29" s="4">
         <v>2</v>
@@ -3335,13 +3338,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D30" s="4">
         <v>20250520</v>
@@ -3350,7 +3353,7 @@
         <v>80525</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G30" s="4">
         <v>3</v>
@@ -3382,7 +3385,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>69</v>
+        <v>266</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -3391,10 +3394,10 @@
     </row>
     <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>32</v>
+        <v>268</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>33</v>
+        <v>271</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>6</v>
@@ -3408,10 +3411,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>34</v>
+        <v>270</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>14</v>
@@ -3422,15 +3425,15 @@
       <c r="E3" s="4"/>
       <c r="G3" s="3" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"');"</f>
-        <v>INSERT INTO AUTH VALUES('AUTH_0001','관리자 권한','Y','1','');</v>
+        <v>INSERT INTO ROLE VALUES('ROLE_0001','관리자 권한','Y','1','');</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>71</v>
+        <v>272</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>14</v>
@@ -3441,7 +3444,7 @@
       <c r="E4" s="4"/>
       <c r="G4" s="3" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A4&amp;"','"&amp;B4&amp;"','"&amp;C4&amp;"','"&amp;D4&amp;"','"&amp;E4&amp;"');"</f>
-        <v>INSERT INTO AUTH VALUES('AUTH_0002','테스트 권한','Y','2','');</v>
+        <v>INSERT INTO ROLE VALUES('ROLE_0002','테스트 권한','Y','2','');</v>
       </c>
     </row>
   </sheetData>
@@ -3464,7 +3467,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>73</v>
+        <v>274</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -3473,7 +3476,7 @@
     </row>
     <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>32</v>
+        <v>267</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>9</v>
@@ -3490,10 +3493,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>14</v>
@@ -3504,12 +3507,12 @@
       <c r="E3" s="4"/>
       <c r="G3" s="3" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"');"</f>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0001','Y','1','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0001','Y','1','');</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>16</v>
@@ -3523,12 +3526,12 @@
       <c r="E4" s="4"/>
       <c r="G4" s="3" t="str">
         <f t="shared" ref="G4:G26" si="0">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A4&amp;"','"&amp;B4&amp;"','"&amp;C4&amp;"','"&amp;D4&amp;"','"&amp;E4&amp;"');"</f>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0002','Y','2','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0002','Y','2','');</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>17</v>
@@ -3542,12 +3545,12 @@
       <c r="E5" s="4"/>
       <c r="G5" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0003','Y','3','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0003','Y','3','');</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>18</v>
@@ -3561,12 +3564,12 @@
       <c r="E6" s="4"/>
       <c r="G6" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0004','Y','4','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0004','Y','4','');</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>15</v>
@@ -3580,12 +3583,12 @@
       <c r="E7" s="4"/>
       <c r="G7" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0005','Y','5','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0005','Y','5','');</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>19</v>
@@ -3599,12 +3602,12 @@
       <c r="E8" s="4"/>
       <c r="G8" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0006','Y','6','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0006','Y','6','');</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>20</v>
@@ -3618,12 +3621,12 @@
       <c r="E9" s="4"/>
       <c r="G9" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0007','Y','7','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0007','Y','7','');</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>21</v>
@@ -3637,12 +3640,12 @@
       <c r="E10" s="4"/>
       <c r="G10" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0008','Y','8','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0008','Y','8','');</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>22</v>
@@ -3656,12 +3659,12 @@
       <c r="E11" s="4"/>
       <c r="G11" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0009','Y','9','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0009','Y','9','');</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>23</v>
@@ -3675,12 +3678,12 @@
       <c r="E12" s="4"/>
       <c r="G12" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0010','Y','10','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0010','Y','10','');</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>24</v>
@@ -3694,12 +3697,12 @@
       <c r="E13" s="4"/>
       <c r="G13" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0011','Y','11','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0011','Y','11','');</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>25</v>
@@ -3713,12 +3716,12 @@
       <c r="E14" s="4"/>
       <c r="G14" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0012','Y','12','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0012','Y','12','');</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>26</v>
@@ -3732,12 +3735,12 @@
       <c r="E15" s="4"/>
       <c r="G15" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0013','Y','13','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0013','Y','13','');</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>27</v>
@@ -3751,12 +3754,12 @@
       <c r="E16" s="4"/>
       <c r="G16" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0014','Y','14','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0014','Y','14','');</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>28</v>
@@ -3770,12 +3773,12 @@
       <c r="E17" s="4"/>
       <c r="G17" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0015','Y','15','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0015','Y','15','');</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>29</v>
@@ -3789,12 +3792,12 @@
       <c r="E18" s="4"/>
       <c r="G18" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0016','Y','16','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0016','Y','16','');</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>30</v>
@@ -3808,15 +3811,15 @@
       <c r="E19" s="4"/>
       <c r="G19" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0017','Y','17','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0017','Y','17','');</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>14</v>
@@ -3827,15 +3830,15 @@
       <c r="E20" s="4"/>
       <c r="G20" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0018','Y','18','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0018','Y','18','');</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>14</v>
@@ -3846,15 +3849,15 @@
       <c r="E21" s="4"/>
       <c r="G21" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0019','Y','19','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0019','Y','19','');</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>14</v>
@@ -3865,15 +3868,15 @@
       <c r="E22" s="4"/>
       <c r="G22" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0020','Y','20','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0020','Y','20','');</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>14</v>
@@ -3884,15 +3887,15 @@
       <c r="E23" s="4"/>
       <c r="G23" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0021','Y','21','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0021','Y','21','');</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>14</v>
@@ -3903,15 +3906,15 @@
       <c r="E24" s="4"/>
       <c r="G24" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0022','Y','22','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0022','Y','22','');</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>14</v>
@@ -3922,15 +3925,15 @@
       <c r="E25" s="4"/>
       <c r="G25" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0023','Y','23','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0023','Y','23','');</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>14</v>
@@ -3941,15 +3944,15 @@
       <c r="E26" s="4"/>
       <c r="G26" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0024','Y','24','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0024','Y','24','');</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>14</v>
@@ -3960,15 +3963,15 @@
       <c r="E27" s="4"/>
       <c r="G27" s="3" t="str">
         <f t="shared" ref="G27" si="1">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A27&amp;"','"&amp;B27&amp;"','"&amp;C27&amp;"','"&amp;D27&amp;"','"&amp;E27&amp;"');"</f>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0025','Y','25','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0025','Y','25','');</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>14</v>
@@ -3979,15 +3982,15 @@
       <c r="E28" s="4"/>
       <c r="G28" s="3" t="str">
         <f t="shared" ref="G28:G29" si="2">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A28&amp;"','"&amp;B28&amp;"','"&amp;C28&amp;"','"&amp;D28&amp;"','"&amp;E28&amp;"');"</f>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0026','Y','26','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0026','Y','26','');</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -3998,15 +4001,15 @@
       <c r="E29" s="4"/>
       <c r="G29" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0027','Y','27','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0027','Y','27','');</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>14</v>
@@ -4017,15 +4020,15 @@
       <c r="E30" s="4"/>
       <c r="G30" s="3" t="str">
         <f t="shared" ref="G30:G31" si="3">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A30&amp;"','"&amp;B30&amp;"','"&amp;C30&amp;"','"&amp;D30&amp;"','"&amp;E30&amp;"');"</f>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0028','Y','28','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0028','Y','28','');</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>14</v>
@@ -4036,15 +4039,15 @@
       <c r="E31" s="4"/>
       <c r="G31" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0029','Y','29','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0029','Y','29','');</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>14</v>
@@ -4055,7 +4058,7 @@
       <c r="E32" s="4"/>
       <c r="G32" s="3" t="str">
         <f t="shared" ref="G32" si="4">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A32&amp;"','"&amp;B32&amp;"','"&amp;C32&amp;"','"&amp;D32&amp;"','"&amp;E32&amp;"');"</f>
-        <v>INSERT INTO MENU_AUTH VALUES('AUTH_0001','MENU_0030','Y','30','');</v>
+        <v>INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0030','Y','30','');</v>
       </c>
     </row>
   </sheetData>
@@ -4078,7 +4081,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>74</v>
+        <v>273</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -4087,7 +4090,7 @@
     </row>
     <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>32</v>
+        <v>267</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>0</v>
@@ -4104,13 +4107,13 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
@@ -4118,7 +4121,7 @@
       <c r="E3" s="4"/>
       <c r="G3" s="3" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"');"</f>
-        <v>INSERT INTO EMP_AUTH VALUES('AUTH_0001','EMP_0001','Y','1','');</v>
+        <v>INSERT INTO EMP_ROLE VALUES('ROLE_0001','EMP_0001','Y','1','');</v>
       </c>
     </row>
   </sheetData>
@@ -4143,7 +4146,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -4163,28 +4166,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>2</v>
@@ -4193,41 +4196,41 @@
         <v>3</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="L3" s="4">
         <v>20230814</v>
@@ -4261,7 +4264,7 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -4273,13 +4276,13 @@
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>4</v>
@@ -4299,20 +4302,20 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4">
         <v>20230814</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G3" s="4">
         <v>1</v>
@@ -4325,20 +4328,20 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4">
         <v>20230814</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G4" s="4">
         <v>2</v>
@@ -4351,20 +4354,20 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4">
         <v>20230814</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G5" s="4">
         <v>3</v>
@@ -4377,20 +4380,20 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4">
         <v>20230814</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G6" s="4">
         <v>4</v>
@@ -4403,20 +4406,20 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4">
         <v>20230814</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G7" s="4">
         <v>5</v>
@@ -4429,20 +4432,20 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4">
         <v>20230814</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G8" s="4">
         <v>6</v>
@@ -4455,20 +4458,20 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4">
         <v>20230814</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G9" s="4">
         <v>7</v>
@@ -4481,20 +4484,20 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4">
         <v>20230814</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G10" s="4">
         <v>8</v>
@@ -4507,20 +4510,20 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4">
         <v>20230814</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G11" s="4">
         <v>9</v>
@@ -4533,20 +4536,20 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4">
         <v>20230814</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G12" s="4">
         <v>10</v>
@@ -4559,20 +4562,20 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4">
         <v>20230814</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G13" s="4">
         <v>11</v>
@@ -4585,20 +4588,20 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4">
         <v>20230814</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G14" s="4">
         <v>12</v>
@@ -4611,20 +4614,20 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4">
         <v>20230814</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G15" s="4">
         <v>13</v>
@@ -4658,7 +4661,7 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -4669,10 +4672,10 @@
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>4</v>
@@ -4692,19 +4695,19 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C3" s="4">
         <v>20230814</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F3" s="4">
         <v>1</v>
@@ -4717,19 +4720,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C4" s="4">
         <v>20230814</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F4" s="4">
         <v>2</v>
@@ -4742,19 +4745,19 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C5" s="4">
         <v>20230814</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F5" s="4">
         <v>3</v>
@@ -4767,19 +4770,19 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C6" s="4">
         <v>20230814</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -4792,19 +4795,19 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C7" s="4">
         <v>20230814</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F7" s="4">
         <v>5</v>
@@ -4817,19 +4820,19 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C8" s="4">
         <v>20230814</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F8" s="4">
         <v>6</v>
@@ -4842,19 +4845,19 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C9" s="4">
         <v>20230814</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F9" s="4">
         <v>7</v>
@@ -4867,19 +4870,19 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C10" s="4">
         <v>20230814</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F10" s="4">
         <v>8</v>
@@ -4892,19 +4895,19 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C11" s="4">
         <v>20230814</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F11" s="4">
         <v>9</v>
@@ -4917,19 +4920,19 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C12" s="4">
         <v>20230814</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F12" s="4">
         <v>10</v>
@@ -4963,7 +4966,7 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -4974,16 +4977,16 @@
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>6</v>
@@ -4997,19 +5000,19 @@
     </row>
     <row r="3" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="D3" s="4">
         <v>20250520</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F3" s="4">
         <v>1</v>
@@ -5072,19 +5075,19 @@
     </row>
     <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="D4" s="4">
         <v>20250520</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F4" s="4">
         <v>2</v>
@@ -5149,19 +5152,19 @@
     </row>
     <row r="5" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D5" s="4">
         <v>20250520</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F5" s="4">
         <v>3</v>
@@ -5226,19 +5229,19 @@
     </row>
     <row r="6" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>229</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>239</v>
       </c>
       <c r="D6" s="4">
         <v>20250520</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -5324,7 +5327,7 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -5343,31 +5346,31 @@
     </row>
     <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>0</v>
@@ -5390,13 +5393,13 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="D3" s="4">
         <v>19900101</v>
@@ -5405,26 +5408,26 @@
         <v>19901231</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H3" s="8">
         <v>0</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N3" s="4">
         <v>1</v>

--- a/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
+++ b/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\knn\Documents\hikr90\02.프로젝트\01.인트라넷\01.설계\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B3395A-18C3-4DA2-9392-8732BFA29734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B28B6E-1897-4B46-B0E9-D9497880E960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="793" xr2:uid="{B204C4DA-9ED1-4F0A-AC7E-C11DE778500E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="286">
   <si>
     <t>EMP_IDX</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1242,6 +1242,37 @@
   <si>
     <t>intrRoleInqy3010.do</t>
   </si>
+  <si>
+    <t>LEAV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CORP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EXP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITEM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intrAprvInqy1020.do</t>
+  </si>
+  <si>
+    <t>intrAprvInqy1021.do</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intrAprvInqy1022.do</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intrAprvInqy1023.do</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1250,7 +1281,7 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="&quot;₩&quot;#,##0;[Red]\-&quot;₩&quot;#,##0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1269,6 +1300,15 @@
     <font>
       <i/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -1319,7 +1359,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1342,13 +1382,34 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1678,16 +1739,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -2543,822 +2604,822 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="10">
         <v>20250520</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="10">
         <v>80516</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="F3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="10">
         <v>1</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3" s="10"/>
       <c r="J3" s="3" t="str">
         <f t="shared" ref="J3:J23" si="0">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"');"</f>
         <v>INSERT INTO COMMCODE VALUES('HIRE_0010','Y','HIRE','20250520','80516','Y','1','');</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="10">
         <v>20250520</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="10">
         <v>80525</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="4">
+      <c r="F4" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="10">
         <v>2</v>
       </c>
-      <c r="H4" s="4"/>
+      <c r="H4" s="10"/>
       <c r="J4" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('HIRE_0020','N','HIRE','20250520','80525','Y','2','');</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="10">
         <v>20250520</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="10">
         <v>80525</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="4">
+      <c r="F5" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="10">
         <v>1</v>
       </c>
-      <c r="H5" s="4"/>
+      <c r="H5" s="10"/>
       <c r="J5" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('STAT_0010','진행','STAT','20250520','80525','Y','1','');</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="10">
         <v>20250520</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="10">
         <v>80525</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="4">
+      <c r="F6" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="10">
         <v>2</v>
       </c>
-      <c r="H6" s="4"/>
+      <c r="H6" s="10"/>
       <c r="J6" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('STAT_0020','완료','STAT','20250520','80525','Y','2','');</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="10">
         <v>20250520</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="10">
         <v>80525</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="4">
+      <c r="F7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="10">
         <v>3</v>
       </c>
-      <c r="H7" s="4"/>
+      <c r="H7" s="10"/>
       <c r="J7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('STAT_0030','보류','STAT','20250520','80525','Y','3','');</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="10">
         <v>20250520</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="10">
         <v>80525</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="4">
+      <c r="F8" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="10">
         <v>1</v>
       </c>
-      <c r="H8" s="4"/>
+      <c r="H8" s="10"/>
       <c r="J8" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('LEAV_0010','연차','LEAV','20250520','80525','Y','1','');</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="10">
         <v>20250520</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="10">
         <v>80525</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="F9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="10">
         <v>2</v>
       </c>
-      <c r="H9" s="4"/>
+      <c r="H9" s="10"/>
       <c r="J9" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('LEAV_0020','병가','LEAV','20250520','80525','Y','2','');</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="10">
         <v>20250520</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="10">
         <v>80525</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="4">
+      <c r="F10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="10">
         <v>3</v>
       </c>
-      <c r="H10" s="4"/>
+      <c r="H10" s="10"/>
       <c r="J10" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('LEAV_0030','경조휴가','LEAV','20250520','80525','Y','3','');</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="10">
         <v>20250520</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="10">
         <v>80525</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="4">
+      <c r="F11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="10">
         <v>4</v>
       </c>
-      <c r="H11" s="4"/>
+      <c r="H11" s="10"/>
       <c r="J11" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('LEAV_0040','반차','LEAV','20250520','80525','Y','4','');</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="10">
         <v>20250520</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="10">
         <v>80525</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="4">
+      <c r="F12" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="10">
         <v>5</v>
       </c>
-      <c r="H12" s="4"/>
+      <c r="H12" s="10"/>
       <c r="J12" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('LEAV_0050','기타','LEAV','20250520','80525','Y','5','');</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="10">
         <v>20250520</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="10">
         <v>80525</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="4">
+      <c r="F13" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="10">
         <v>1</v>
       </c>
-      <c r="H13" s="4"/>
+      <c r="H13" s="10"/>
       <c r="J13" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('PAY_0010','현금','PAY','20250520','80525','Y','1','');</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="10">
         <v>20250520</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="10">
         <v>80525</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" s="4">
+      <c r="F14" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="10">
         <v>2</v>
       </c>
-      <c r="H14" s="4"/>
+      <c r="H14" s="10"/>
       <c r="J14" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('PAY_0020','개인카드','PAY','20250520','80525','Y','2','');</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="10">
         <v>20250520</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="10">
         <v>80525</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="4">
+      <c r="F15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="10">
         <v>3</v>
       </c>
-      <c r="H15" s="4"/>
+      <c r="H15" s="10"/>
       <c r="J15" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('PAY_0030','전도금','PAY','20250520','80525','Y','3','');</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="10">
         <v>20250520</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="10">
         <v>80525</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16" s="4">
+      <c r="F16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="10">
         <v>1</v>
       </c>
-      <c r="H16" s="4"/>
+      <c r="H16" s="10"/>
       <c r="J16" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('TYPE_0010','기안','TYPE','20250520','80525','Y','1','');</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="10">
         <v>20250520</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="10">
         <v>80525</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" s="4">
+      <c r="F17" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="10">
         <v>2</v>
       </c>
-      <c r="H17" s="4"/>
+      <c r="H17" s="10"/>
       <c r="J17" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('TYPE_0020','결재','TYPE','20250520','80525','Y','2','');</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="10">
         <v>20250520</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="10">
         <v>80525</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18" s="4">
+      <c r="F18" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="10">
         <v>3</v>
       </c>
-      <c r="H18" s="4"/>
+      <c r="H18" s="10"/>
       <c r="J18" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('TYPE_0030','참조','TYPE','20250520','80525','Y','3','');</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="10">
         <v>20250520</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="10">
         <v>80525</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G19" s="4">
+      <c r="F19" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="10">
         <v>1</v>
       </c>
-      <c r="H19" s="4"/>
+      <c r="H19" s="10"/>
       <c r="J19" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('REQ_0010','반입','REQ','20250520','80525','Y','1','');</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="10">
         <v>20250520</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="10">
         <v>80525</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20" s="4">
+      <c r="F20" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="10">
         <v>2</v>
       </c>
-      <c r="H20" s="4"/>
+      <c r="H20" s="10"/>
       <c r="J20" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('REQ_0020','반출','REQ','20250520','80525','Y','2','');</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="10">
         <v>20250520</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="10">
         <v>80525</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G21" s="4">
+      <c r="F21" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="10">
         <v>1</v>
       </c>
-      <c r="H21" s="4"/>
+      <c r="H21" s="10"/>
       <c r="J21" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('STEP_0010','결재진행중','STEP','20250520','80525','Y','1','');</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="10">
         <v>20250520</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="10">
         <v>80525</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G22" s="4">
+      <c r="F22" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="10">
         <v>2</v>
       </c>
-      <c r="H22" s="4"/>
+      <c r="H22" s="10"/>
       <c r="J22" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('STEP_0020','결재완료','STEP','20250520','80525','Y','2','');</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="10">
         <v>20250520</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="10">
         <v>80525</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G23" s="4">
+      <c r="F23" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="10">
         <v>3</v>
       </c>
-      <c r="H23" s="4"/>
+      <c r="H23" s="10"/>
       <c r="J23" s="3" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO COMMCODE VALUES('STEP_0030','결재반송','STEP','20250520','80525','Y','3','');</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="10">
         <v>20250520</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="10">
         <v>80525</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" s="4">
+      <c r="F24" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="10">
         <v>4</v>
       </c>
-      <c r="H24" s="4"/>
+      <c r="H24" s="10"/>
       <c r="J24" s="3" t="str">
         <f t="shared" ref="J24" si="1">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A24&amp;"','"&amp;B24&amp;"','"&amp;C24&amp;"','"&amp;D24&amp;"','"&amp;E24&amp;"','"&amp;F24&amp;"','"&amp;G24&amp;"','"&amp;H24&amp;"');"</f>
         <v>INSERT INTO COMMCODE VALUES('STEP_0040','결재취소','STEP','20250520','80525','Y','4','');</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="10">
         <v>20250520</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="10">
         <v>80525</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G25" s="4">
+      <c r="F25" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="10">
         <v>1</v>
       </c>
-      <c r="H25" s="4"/>
+      <c r="H25" s="10"/>
       <c r="J25" s="3" t="str">
         <f t="shared" ref="J25:J26" si="2">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A25&amp;"','"&amp;B25&amp;"','"&amp;C25&amp;"','"&amp;D25&amp;"','"&amp;E25&amp;"','"&amp;F25&amp;"','"&amp;G25&amp;"','"&amp;H25&amp;"');"</f>
         <v>INSERT INTO COMMCODE VALUES('RSLT_0010','승인','RSLT','20250520','80525','Y','1','');</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="10">
         <v>20250520</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="10">
         <v>80525</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G26" s="4">
+      <c r="F26" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" s="10">
         <v>2</v>
       </c>
-      <c r="H26" s="4"/>
+      <c r="H26" s="10"/>
       <c r="J26" s="3" t="str">
         <f t="shared" si="2"/>
         <v>INSERT INTO COMMCODE VALUES('RSLT_0020','반송','RSLT','20250520','80525','Y','2','');</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="10">
         <v>20250520</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="10">
         <v>80525</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G27" s="4">
+      <c r="F27" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" s="10">
         <v>3</v>
       </c>
-      <c r="H27" s="4"/>
+      <c r="H27" s="10"/>
       <c r="J27" s="3" t="str">
         <f t="shared" ref="J27:J29" si="3">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A27&amp;"','"&amp;B27&amp;"','"&amp;C27&amp;"','"&amp;D27&amp;"','"&amp;E27&amp;"','"&amp;F27&amp;"','"&amp;G27&amp;"','"&amp;H27&amp;"');"</f>
         <v>INSERT INTO COMMCODE VALUES('RSLT_0030','취소','RSLT','20250520','80525','Y','3','');</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="10">
         <v>20250520</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="10">
         <v>80525</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G28" s="4">
+      <c r="F28" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" s="10">
         <v>1</v>
       </c>
-      <c r="H28" s="4"/>
+      <c r="H28" s="10"/>
       <c r="J28" s="3" t="str">
         <f t="shared" si="3"/>
         <v>INSERT INTO COMMCODE VALUES('LOC_0010','회의실 (대)','LOC','20250520','80525','Y','1','');</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="10">
         <v>20250520</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="10">
         <v>80525</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G29" s="4">
+      <c r="F29" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29" s="10">
         <v>2</v>
       </c>
-      <c r="H29" s="4"/>
+      <c r="H29" s="10"/>
       <c r="J29" s="3" t="str">
         <f t="shared" si="3"/>
         <v>INSERT INTO COMMCODE VALUES('LOC_0020','회의실 (중)','LOC','20250520','80525','Y','2','');</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="10">
         <v>20250520</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="10">
         <v>80525</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G30" s="4">
+      <c r="F30" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G30" s="10">
         <v>3</v>
       </c>
-      <c r="H30" s="4"/>
+      <c r="H30" s="10"/>
       <c r="J30" s="3" t="str">
         <f t="shared" ref="J30" si="4">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A30&amp;"','"&amp;B30&amp;"','"&amp;C30&amp;"','"&amp;D30&amp;"','"&amp;E30&amp;"','"&amp;F30&amp;"','"&amp;G30&amp;"','"&amp;H30&amp;"');"</f>
         <v>INSERT INTO COMMCODE VALUES('LOC_0030','회의실 (소)','LOC','20250520','80525','Y','3','');</v>
@@ -3384,13 +3445,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -3466,13 +3527,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -4080,13 +4141,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -4145,21 +4206,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -4263,16 +4324,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -4660,15 +4721,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -4957,70 +5018,80 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA0932ED-ACD7-45D7-AA89-FB38B3C13900}">
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="7" width="17.625" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="1" max="3" width="17.625" style="14" customWidth="1"/>
+    <col min="4" max="4" width="61.75" style="14" customWidth="1"/>
+    <col min="5" max="5" width="17.875" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="17.625" style="14" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-    </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="D3" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="D3" s="4">
-        <v>20250520</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="4">
+      <c r="E3" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="10">
         <v>1</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="I3" s="3" t="str">
-        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"',''"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"');"</f>
-        <v>INSERT INTO TEMPLATE VALUES('TEMP_0001','휴가 신청서','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;휴가 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+      <c r="H3" s="10"/>
+      <c r="J3" s="15" t="str">
+        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"',''"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"');"</f>
+        <v>INSERT INTO TEMPLATE VALUES('TEMP_0001','휴가 신청서','LEAV','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;휴가 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
 	&lt;tbody&gt;
 		&lt;tr&gt;
@@ -5070,31 +5141,34 @@
 			&lt;/td&gt;
 		&lt;/tr&gt;
 	&lt;/tbody&gt;
-&lt;/table&gt;','20250520',''Y','1','');</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+&lt;/table&gt;',''Y','1','');</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="D4" s="4">
-        <v>20250520</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="E4" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="10">
         <v>2</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="I4" s="3" t="str">
-        <f t="shared" ref="I4:I6" si="0">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A4&amp;"','"&amp;B4&amp;"','"&amp;C4&amp;"','"&amp;D4&amp;"',''"&amp;E4&amp;"','"&amp;F4&amp;"','"&amp;G4&amp;"');"</f>
+      <c r="H4" s="10"/>
+      <c r="J4" s="15" t="str">
+        <f t="shared" ref="J4:J6" si="0">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A4&amp;"','"&amp;B4&amp;"','"&amp;D4&amp;"','"&amp;E4&amp;"',''"&amp;F4&amp;"','"&amp;G4&amp;"','"&amp;H4&amp;"');"</f>
         <v>INSERT INTO TEMPLATE VALUES('TEMP_0002','가지급결의서','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;가지급결의서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
 	&lt;tbody&gt;
@@ -5147,30 +5221,33 @@
 			&lt;/td&gt;
 		&lt;/tr&gt;
 	&lt;/tbody&gt;
-&lt;/table&gt;','20250520',''Y','2','');</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+&lt;/table&gt;','intrAprvInqy1021.do',''Y','2','');</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="D5" s="4">
-        <v>20250520</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="4">
+      <c r="E5" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="10">
         <v>3</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="I5" s="3" t="str">
+      <c r="H5" s="10"/>
+      <c r="J5" s="15" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO TEMPLATE VALUES('TEMP_0003','물품반출입 신청서','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;물품반출입 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
@@ -5224,30 +5301,33 @@
 			&lt;/td&gt;
 		&lt;/tr&gt;
 	&lt;/tbody&gt;
-&lt;/table&gt;','20250520',''Y','3','');</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+&lt;/table&gt;','intrAprvInqy1022.do',''Y','3','');</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="D6" s="4">
-        <v>20250520</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="E6" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="10">
         <v>4</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="I6" s="3" t="str">
+      <c r="H6" s="10"/>
+      <c r="J6" s="15" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO TEMPLATE VALUES('TEMP_0004','법인카드 정산서','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;법인카드 정산서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
@@ -5299,17 +5379,17 @@
 			&lt;/td&gt;
 		&lt;/tr&gt;
 	&lt;/tbody&gt;
-&lt;/table&gt;','20250520',''Y','4','');</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+&lt;/table&gt;','intrAprvInqy1023.do',''Y','4','');</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5319,121 +5399,121 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{877A2008-3B0E-4DFC-9F39-16C9B5BC3402}">
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="15" width="17.625" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="1" max="15" width="17.625" style="14" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-    </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+    </row>
+    <row r="2" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="10">
         <v>19900101</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="10">
         <v>19901231</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="12">
         <v>0</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
+      <c r="I3" s="10"/>
+      <c r="J3" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="M3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" s="4">
+      <c r="M3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="10">
         <v>1</v>
       </c>
-      <c r="O3" s="4"/>
-      <c r="Q3" s="3" t="str">
+      <c r="O3" s="10"/>
+      <c r="Q3" s="15" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;L3&amp;"','"&amp;M3&amp;"','"&amp;N3&amp;"','"&amp;O3&amp;"');"</f>
         <v>INSERT INTO PROJECT VALUES('PROJ_0001','내부 프로젝트','내부 프로젝트','19900101','000000','Y','1','');</v>
       </c>

--- a/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
+++ b/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="7"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="MENU" sheetId="1" state="visible" r:id="rId2"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
   <si>
     <t>MENU</t>
   </si>
@@ -406,6 +406,9 @@
   </si>
   <si>
     <t>jtax90@naver.com</t>
+  </si>
+  <si>
+    <t>+SsCQIbDOBIORGzUhrNPHA==</t>
   </si>
   <si>
     <t>ORG</t>
@@ -2606,7 +2609,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1">
       <c r="A1" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -2618,19 +2621,19 @@
     </row>
     <row r="2" s="2" customFormat="1">
       <c r="A2" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>6</v>
@@ -2644,13 +2647,13 @@
     </row>
     <row r="3">
       <c r="A3" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>96</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D3" s="12">
         <v>20250520</v>
@@ -2672,13 +2675,13 @@
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>229</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>228</v>
       </c>
       <c r="D4" s="12">
         <v>20250520</v>
@@ -2700,13 +2703,13 @@
     </row>
     <row r="5">
       <c r="A5" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D5" s="12">
         <v>20250520</v>
@@ -2728,13 +2731,13 @@
     </row>
     <row r="6">
       <c r="A6" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D6" s="12">
         <v>20250520</v>
@@ -2756,13 +2759,13 @@
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>237</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>236</v>
       </c>
       <c r="D7" s="12">
         <v>20250520</v>
@@ -2784,13 +2787,13 @@
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D8" s="12">
         <v>20250520</v>
@@ -2812,13 +2815,13 @@
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>242</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>241</v>
       </c>
       <c r="D9" s="12">
         <v>20250520</v>
@@ -2840,13 +2843,13 @@
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D10" s="12">
         <v>20250520</v>
@@ -2868,13 +2871,13 @@
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D11" s="12">
         <v>20250520</v>
@@ -2896,13 +2899,13 @@
     </row>
     <row r="12">
       <c r="A12" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D12" s="12">
         <v>20250520</v>
@@ -2924,13 +2927,13 @@
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D13" s="12">
         <v>20250520</v>
@@ -2952,13 +2955,13 @@
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>253</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>252</v>
       </c>
       <c r="D14" s="12">
         <v>20250520</v>
@@ -2980,13 +2983,13 @@
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D15" s="12">
         <v>20250520</v>
@@ -3008,13 +3011,13 @@
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D16" s="12">
         <v>20250520</v>
@@ -3036,13 +3039,13 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>260</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>259</v>
       </c>
       <c r="D17" s="12">
         <v>20250520</v>
@@ -3064,13 +3067,13 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D18" s="12">
         <v>20250520</v>
@@ -3092,13 +3095,13 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D19" s="12">
         <v>20250520</v>
@@ -3120,13 +3123,13 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>267</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>266</v>
       </c>
       <c r="D20" s="12">
         <v>20250520</v>
@@ -3148,13 +3151,13 @@
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D21" s="12">
         <v>20250520</v>
@@ -3176,13 +3179,13 @@
     </row>
     <row r="22">
       <c r="A22" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>272</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="D22" s="12">
         <v>20250520</v>
@@ -3204,13 +3207,13 @@
     </row>
     <row r="23">
       <c r="A23" s="12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D23" s="12">
         <v>20250520</v>
@@ -3232,13 +3235,13 @@
     </row>
     <row r="24">
       <c r="A24" s="12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D24" s="12">
         <v>20250520</v>
@@ -3260,13 +3263,13 @@
     </row>
     <row r="25">
       <c r="A25" s="12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D25" s="12">
         <v>20250520</v>
@@ -3288,13 +3291,13 @@
     </row>
     <row r="26">
       <c r="A26" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>281</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>280</v>
       </c>
       <c r="D26" s="12">
         <v>20250520</v>
@@ -3316,13 +3319,13 @@
     </row>
     <row r="27">
       <c r="A27" s="12" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D27" s="12">
         <v>20250520</v>
@@ -3344,13 +3347,13 @@
     </row>
     <row r="28">
       <c r="A28" s="12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D28" s="12">
         <v>20250520</v>
@@ -3372,13 +3375,13 @@
     </row>
     <row r="29">
       <c r="A29" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C29" s="12" t="s">
         <v>288</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>287</v>
       </c>
       <c r="D29" s="12">
         <v>20250520</v>
@@ -3400,13 +3403,13 @@
     </row>
     <row r="30">
       <c r="A30" s="12" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D30" s="12">
         <v>20250520</v>
@@ -4295,7 +4298,7 @@
         <v>124</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="L3" s="5">
         <v>20230814</v>
@@ -4303,7 +4306,7 @@
       <c r="M3" s="5"/>
       <c r="O3" s="6" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"','"&amp;I3&amp;"','"&amp;J3&amp;"','"&amp;K3&amp;"','"&amp;L3&amp;"','"&amp;M3&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO EMP_INFO VALUES('EMP_0001','ORG_0001','RANK_0001','ADMIN','Y','01077945147','','','jtax90@naver.com','ADMIN','ADMIN','20230814','');</v>
+        <v xml:space="preserve">INSERT INTO EMP_INFO VALUES('EMP_0001','ORG_0001','RANK_0001','ADMIN','Y','01077945147','','','jtax90@naver.com','ADMIN','+SsCQIbDOBIORGzUhrNPHA==','20230814','');</v>
       </c>
     </row>
   </sheetData>
@@ -4327,7 +4330,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -4342,16 +4345,16 @@
         <v>109</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>6</v>
@@ -4368,14 +4371,14 @@
         <v>122</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5">
         <v>20230814</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>11</v>
@@ -4391,17 +4394,17 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5">
         <v>20230814</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>11</v>
@@ -4417,17 +4420,17 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5">
         <v>20230814</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>11</v>
@@ -4443,17 +4446,17 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5">
         <v>20230814</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>11</v>
@@ -4469,17 +4472,17 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5">
         <v>20230814</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>11</v>
@@ -4495,17 +4498,17 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5">
         <v>20230814</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>11</v>
@@ -4521,17 +4524,17 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5">
         <v>20230814</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>11</v>
@@ -4547,17 +4550,17 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5">
         <v>20230814</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>11</v>
@@ -4573,17 +4576,17 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5">
         <v>20230814</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>11</v>
@@ -4599,17 +4602,17 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5">
         <v>20230814</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>11</v>
@@ -4625,17 +4628,17 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5">
         <v>20230814</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>11</v>
@@ -4651,17 +4654,17 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5">
         <v>20230814</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>11</v>
@@ -4677,17 +4680,17 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5">
         <v>20230814</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>11</v>
@@ -4722,7 +4725,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -4736,13 +4739,13 @@
         <v>110</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>6</v>
@@ -4759,13 +4762,13 @@
         <v>123</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C3" s="5">
         <v>20230814</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>11</v>
@@ -4781,16 +4784,16 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C4" s="5">
         <v>20230814</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>11</v>
@@ -4806,16 +4809,16 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C5" s="5">
         <v>20230814</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>11</v>
@@ -4831,16 +4834,16 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C6" s="5">
         <v>20230814</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>11</v>
@@ -4856,16 +4859,16 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C7" s="5">
         <v>20230814</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>11</v>
@@ -4881,16 +4884,16 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C8" s="5">
         <v>20230814</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>11</v>
@@ -4906,16 +4909,16 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C9" s="5">
         <v>20230814</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>11</v>
@@ -4931,16 +4934,16 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C10" s="5">
         <v>20230814</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>11</v>
@@ -4956,16 +4959,16 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C11" s="5">
         <v>20230814</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>11</v>
@@ -4981,16 +4984,16 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C12" s="5">
         <v>20230814</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>11</v>
@@ -5029,7 +5032,7 @@
   <sheetData>
     <row r="1" s="9" customFormat="1">
       <c r="A1" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -5042,22 +5045,22 @@
     </row>
     <row r="2" s="9" customFormat="1">
       <c r="A2" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>6</v>
@@ -5071,22 +5074,22 @@
     </row>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>11</v>
@@ -5153,22 +5156,22 @@
     </row>
     <row r="4" ht="16.5" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>11</v>
@@ -5237,22 +5240,22 @@
     </row>
     <row r="5" ht="16.5" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>11</v>
@@ -5321,22 +5324,22 @@
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>11</v>
@@ -5427,7 +5430,7 @@
   <sheetData>
     <row r="1" s="9" customFormat="1">
       <c r="A1" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -5446,40 +5449,40 @@
     </row>
     <row r="2" s="9" customFormat="1">
       <c r="A2" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J2" s="11" t="s">
         <v>106</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>6</v>
@@ -5493,13 +5496,13 @@
     </row>
     <row r="3">
       <c r="A3" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D3" s="12">
         <v>19900101</v>
@@ -5508,7 +5511,7 @@
         <v>19901231</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>121</v>
@@ -5521,10 +5524,10 @@
         <v>121</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M3" s="12" t="s">
         <v>11</v>
@@ -5534,8 +5537,8 @@
       </c>
       <c r="O3" s="12"/>
       <c r="Q3" s="14" t="str">
-        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;L3&amp;"','"&amp;M3&amp;"','"&amp;N3&amp;"','"&amp;O3&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO PROJECT VALUES('PROJ_0001','내부 프로젝트','내부 프로젝트','19900101','000000','Y','1','');</v>
+        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"','"&amp;I3&amp;"','"&amp;J3&amp;"','"&amp;K3&amp;"','"&amp;L3&amp;"','"&amp;M3&amp;"','"&amp;N3&amp;"','"&amp;O3&amp;"');"</f>
+        <v xml:space="preserve">INSERT INTO PROJECT VALUES('PROJ_0001','내부 프로젝트','내부 프로젝트','19900101','19901231','STAT_0020','EMP_0001','0','','EMP_0001','000000','000000','Y','1','');</v>
       </c>
     </row>
   </sheetData>

--- a/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
+++ b/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="MENU" sheetId="1" state="visible" r:id="rId2"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
   <si>
     <t>MENU</t>
   </si>
@@ -918,7 +918,7 @@
     <t>HIRE_0010</t>
   </si>
   <si>
-    <t>HIRE</t>
+    <t>Hire</t>
   </si>
   <si>
     <t>HIRE_0020</t>
@@ -933,7 +933,7 @@
     <t>진행</t>
   </si>
   <si>
-    <t>STAT</t>
+    <t>Stat</t>
   </si>
   <si>
     <t>STAT_0020</t>
@@ -942,9 +942,6 @@
     <t>완료</t>
   </si>
   <si>
-    <t>STAT</t>
-  </si>
-  <si>
     <t>STAT_0030</t>
   </si>
   <si>
@@ -957,7 +954,7 @@
     <t>연차</t>
   </si>
   <si>
-    <t>LEAV</t>
+    <t>Leav</t>
   </si>
   <si>
     <t>LEAV_0020</t>
@@ -990,7 +987,7 @@
     <t>현금</t>
   </si>
   <si>
-    <t>PAY</t>
+    <t>Pay</t>
   </si>
   <si>
     <t>PAY_0020</t>
@@ -1011,7 +1008,7 @@
     <t>기안</t>
   </si>
   <si>
-    <t>TYPE</t>
+    <t>Type</t>
   </si>
   <si>
     <t>TYPE_0020</t>
@@ -1032,7 +1029,7 @@
     <t>반입</t>
   </si>
   <si>
-    <t>REQ</t>
+    <t>Req</t>
   </si>
   <si>
     <t>REQ_0020</t>
@@ -1047,7 +1044,7 @@
     <t>결재진행중</t>
   </si>
   <si>
-    <t>STEP</t>
+    <t>Step</t>
   </si>
   <si>
     <t>STEP_0020</t>
@@ -1074,7 +1071,7 @@
     <t>승인</t>
   </si>
   <si>
-    <t>RSLT</t>
+    <t>Rslt</t>
   </si>
   <si>
     <t>RSLT_0020</t>
@@ -1095,7 +1092,7 @@
     <t xml:space="preserve">회의실 (대)</t>
   </si>
   <si>
-    <t>LOC</t>
+    <t>Loc</t>
   </si>
   <si>
     <t>LOC_0020</t>
@@ -1117,15 +1114,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₩&quot;#,##0;[Red]\-&quot;₩&quot;#,##0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
-      <sz val="11.000000"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1135,8 +1125,7 @@
       <i/>
       <sz val="10.000000"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
+      <name val="돋움"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1181,7 +1170,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="10">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1206,31 +1195,10 @@
     <xf fontId="1" fillId="0" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2608,825 +2576,825 @@
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" s="2" customFormat="1">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="5">
         <v>20250520</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="5">
         <v>80516</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="12">
+      <c r="F3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="5">
         <v>1</v>
       </c>
-      <c r="H3" s="12"/>
+      <c r="H3" s="5"/>
       <c r="J3" s="6" t="str">
-        <f t="shared" ref="J3:J23" si="8">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('HIRE_0010','Y','HIRE','20250520','80516','Y','1','');</v>
+        <f t="shared" ref="J3:J23" si="9">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"');"</f>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('HIRE_0010','Y','Hire','20250520','80516','Y','1','');</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="5">
         <v>20250520</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="5">
         <v>80525</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="12">
+      <c r="F4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="5">
         <v>2</v>
       </c>
-      <c r="H4" s="12"/>
+      <c r="H4" s="5"/>
       <c r="J4" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('HIRE_0020','N','HIRE','20250520','80525','Y','2','');</v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('HIRE_0020','N','Hire','20250520','80525','Y','2','');</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="5">
         <v>20250520</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="5">
         <v>80525</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="12">
+      <c r="F5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="5">
         <v>1</v>
       </c>
-      <c r="H5" s="12"/>
+      <c r="H5" s="5"/>
       <c r="J5" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STAT_0010','진행','STAT','20250520','80525','Y','1','');</v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STAT_0010','진행','Stat','20250520','80525','Y','1','');</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D6" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E6" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="J6" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STAT_0020','완료','Stat','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D6" s="12">
+      <c r="B7" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D7" s="5">
         <v>20250520</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E7" s="5">
         <v>80525</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="12">
+      <c r="F7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="5">
+        <v>3</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="J7" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STAT_0030','보류','Stat','20250520','80525','Y','3','');</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D8" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E8" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="J8" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LEAV_0010','연차','Leav','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D9" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E9" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="5">
         <v>2</v>
       </c>
-      <c r="H6" s="12"/>
-      <c r="J6" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STAT_0020','완료','STAT','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="D7" s="12">
+      <c r="H9" s="5"/>
+      <c r="J9" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LEAV_0020','병가','Leav','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D10" s="5">
         <v>20250520</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E10" s="5">
         <v>80525</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="12">
+      <c r="F10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="5">
         <v>3</v>
       </c>
-      <c r="H7" s="12"/>
-      <c r="J7" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STAT_0030','보류','STAT','20250520','80525','Y','3','');</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="B8" s="12" t="s">
+      <c r="H10" s="5"/>
+      <c r="J10" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LEAV_0030','경조휴가','Leav','20250520','80525','Y','3','');</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="D8" s="12">
+      <c r="D11" s="5">
         <v>20250520</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E11" s="5">
         <v>80525</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="12">
+      <c r="F11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="5">
+        <v>4</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="J11" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LEAV_0040','반차','Leav','20250520','80525','Y','4','');</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D12" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E12" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="5">
+        <v>5</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="J12" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LEAV_0050','기타','Leav','20250520','80525','Y','5','');</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D13" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E13" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="5">
         <v>1</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="J8" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LEAV_0010','연차','LEAV','20250520','80525','Y','1','');</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="D9" s="12">
+      <c r="H13" s="5"/>
+      <c r="J13" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('PAY_0010','현금','Pay','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D14" s="5">
         <v>20250520</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E14" s="5">
         <v>80525</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="12">
+      <c r="F14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="5">
         <v>2</v>
       </c>
-      <c r="H9" s="12"/>
-      <c r="J9" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LEAV_0020','병가','LEAV','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="D10" s="12">
+      <c r="H14" s="5"/>
+      <c r="J14" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('PAY_0020','개인카드','Pay','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D15" s="5">
         <v>20250520</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E15" s="5">
         <v>80525</v>
       </c>
-      <c r="F10" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="12">
+      <c r="F15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="5">
         <v>3</v>
       </c>
-      <c r="H10" s="12"/>
-      <c r="J10" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LEAV_0030','경조휴가','LEAV','20250520','80525','Y','3','');</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="D11" s="12">
+      <c r="H15" s="5"/>
+      <c r="J15" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('PAY_0030','전도금','Pay','20250520','80525','Y','3','');</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D16" s="5">
         <v>20250520</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E16" s="5">
         <v>80525</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="12">
+      <c r="F16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="5">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="J16" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('TYPE_0010','기안','Type','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D17" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E17" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="5">
+        <v>2</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="J17" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('TYPE_0020','결재','Type','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D18" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E18" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="5">
+        <v>3</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="J18" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('TYPE_0030','참조','Type','20250520','80525','Y','3','');</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D19" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E19" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="5">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="J19" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('REQ_0010','반입','Req','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D20" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E20" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="5">
+        <v>2</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="J20" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('REQ_0020','반출','Req','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D21" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E21" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="5">
+        <v>1</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="J21" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STEP_0010','결재진행중','Step','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D22" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E22" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="5">
+        <v>2</v>
+      </c>
+      <c r="H22" s="5"/>
+      <c r="J22" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STEP_0020','결재완료','Step','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D23" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E23" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="5">
+        <v>3</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="J23" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STEP_0030','결재반송','Step','20250520','80525','Y','3','');</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D24" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E24" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="5">
         <v>4</v>
       </c>
-      <c r="H11" s="12"/>
-      <c r="J11" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LEAV_0040','반차','LEAV','20250520','80525','Y','4','');</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="D12" s="12">
+      <c r="H24" s="5"/>
+      <c r="J24" s="6" t="str">
+        <f t="shared" ref="J24:J30" si="10">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A24&amp;"','"&amp;B24&amp;"','"&amp;C24&amp;"','"&amp;D24&amp;"','"&amp;E24&amp;"','"&amp;F24&amp;"','"&amp;G24&amp;"','"&amp;H24&amp;"');"</f>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STEP_0040','결재취소','Step','20250520','80525','Y','4','');</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D25" s="5">
         <v>20250520</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E25" s="5">
         <v>80525</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="12">
-        <v>5</v>
-      </c>
-      <c r="H12" s="12"/>
-      <c r="J12" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LEAV_0050','기타','LEAV','20250520','80525','Y','5','');</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="D13" s="12">
+      <c r="F25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="5">
+        <v>1</v>
+      </c>
+      <c r="H25" s="5"/>
+      <c r="J25" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('RSLT_0010','승인','Rslt','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D26" s="5">
         <v>20250520</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E26" s="5">
         <v>80525</v>
       </c>
-      <c r="F13" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="F26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="5">
+        <v>2</v>
+      </c>
+      <c r="H26" s="5"/>
+      <c r="J26" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('RSLT_0020','반송','Rslt','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D27" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E27" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="5">
+        <v>3</v>
+      </c>
+      <c r="H27" s="5"/>
+      <c r="J27" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('RSLT_0030','취소','Rslt','20250520','80525','Y','3','');</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D28" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E28" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="5">
         <v>1</v>
       </c>
-      <c r="H13" s="12"/>
-      <c r="J13" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('PAY_0010','현금','PAY','20250520','80525','Y','1','');</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="D14" s="12">
+      <c r="H28" s="5"/>
+      <c r="J28" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LOC_0010','회의실 (대)','Loc','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D29" s="5">
         <v>20250520</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E29" s="5">
         <v>80525</v>
       </c>
-      <c r="F14" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="12">
+      <c r="F29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="5">
         <v>2</v>
       </c>
-      <c r="H14" s="12"/>
-      <c r="J14" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('PAY_0020','개인카드','PAY','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="D15" s="12">
+      <c r="H29" s="5"/>
+      <c r="J29" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LOC_0020','회의실 (중)','Loc','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D30" s="5">
         <v>20250520</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E30" s="5">
         <v>80525</v>
       </c>
-      <c r="F15" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="12">
+      <c r="F30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="5">
         <v>3</v>
       </c>
-      <c r="H15" s="12"/>
-      <c r="J15" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('PAY_0030','전도금','PAY','20250520','80525','Y','3','');</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="D16" s="12">
-        <v>20250520</v>
-      </c>
-      <c r="E16" s="12">
-        <v>80525</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="12">
-        <v>1</v>
-      </c>
-      <c r="H16" s="12"/>
-      <c r="J16" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('TYPE_0010','기안','TYPE','20250520','80525','Y','1','');</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="D17" s="12">
-        <v>20250520</v>
-      </c>
-      <c r="E17" s="12">
-        <v>80525</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="12">
-        <v>2</v>
-      </c>
-      <c r="H17" s="12"/>
-      <c r="J17" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('TYPE_0020','결재','TYPE','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="D18" s="12">
-        <v>20250520</v>
-      </c>
-      <c r="E18" s="12">
-        <v>80525</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="12">
-        <v>3</v>
-      </c>
-      <c r="H18" s="12"/>
-      <c r="J18" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('TYPE_0030','참조','TYPE','20250520','80525','Y','3','');</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="D19" s="12">
-        <v>20250520</v>
-      </c>
-      <c r="E19" s="12">
-        <v>80525</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" s="12">
-        <v>1</v>
-      </c>
-      <c r="H19" s="12"/>
-      <c r="J19" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('REQ_0010','반입','REQ','20250520','80525','Y','1','');</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="D20" s="12">
-        <v>20250520</v>
-      </c>
-      <c r="E20" s="12">
-        <v>80525</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" s="12">
-        <v>2</v>
-      </c>
-      <c r="H20" s="12"/>
-      <c r="J20" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('REQ_0020','반출','REQ','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="D21" s="12">
-        <v>20250520</v>
-      </c>
-      <c r="E21" s="12">
-        <v>80525</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21" s="12">
-        <v>1</v>
-      </c>
-      <c r="H21" s="12"/>
-      <c r="J21" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STEP_0010','결재진행중','STEP','20250520','80525','Y','1','');</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="D22" s="12">
-        <v>20250520</v>
-      </c>
-      <c r="E22" s="12">
-        <v>80525</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="12">
-        <v>2</v>
-      </c>
-      <c r="H22" s="12"/>
-      <c r="J22" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STEP_0020','결재완료','STEP','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="D23" s="12">
-        <v>20250520</v>
-      </c>
-      <c r="E23" s="12">
-        <v>80525</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" s="12">
-        <v>3</v>
-      </c>
-      <c r="H23" s="12"/>
-      <c r="J23" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STEP_0030','결재반송','STEP','20250520','80525','Y','3','');</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="D24" s="12">
-        <v>20250520</v>
-      </c>
-      <c r="E24" s="12">
-        <v>80525</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24" s="12">
-        <v>4</v>
-      </c>
-      <c r="H24" s="12"/>
-      <c r="J24" s="6" t="str">
-        <f t="shared" ref="J24:J30" si="9">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A24&amp;"','"&amp;B24&amp;"','"&amp;C24&amp;"','"&amp;D24&amp;"','"&amp;E24&amp;"','"&amp;F24&amp;"','"&amp;G24&amp;"','"&amp;H24&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STEP_0040','결재취소','STEP','20250520','80525','Y','4','');</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="D25" s="12">
-        <v>20250520</v>
-      </c>
-      <c r="E25" s="12">
-        <v>80525</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25" s="12">
-        <v>1</v>
-      </c>
-      <c r="H25" s="12"/>
-      <c r="J25" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('RSLT_0010','승인','RSLT','20250520','80525','Y','1','');</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="D26" s="12">
-        <v>20250520</v>
-      </c>
-      <c r="E26" s="12">
-        <v>80525</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" s="12">
-        <v>2</v>
-      </c>
-      <c r="H26" s="12"/>
-      <c r="J26" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('RSLT_0020','반송','RSLT','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="D27" s="12">
-        <v>20250520</v>
-      </c>
-      <c r="E27" s="12">
-        <v>80525</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27" s="12">
-        <v>3</v>
-      </c>
-      <c r="H27" s="12"/>
-      <c r="J27" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('RSLT_0030','취소','RSLT','20250520','80525','Y','3','');</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="D28" s="12">
-        <v>20250520</v>
-      </c>
-      <c r="E28" s="12">
-        <v>80525</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" s="12">
-        <v>1</v>
-      </c>
-      <c r="H28" s="12"/>
-      <c r="J28" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LOC_0010','회의실 (대)','LOC','20250520','80525','Y','1','');</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="D29" s="12">
-        <v>20250520</v>
-      </c>
-      <c r="E29" s="12">
-        <v>80525</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="12">
-        <v>2</v>
-      </c>
-      <c r="H29" s="12"/>
-      <c r="J29" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LOC_0020','회의실 (중)','LOC','20250520','80525','Y','2','');</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="D30" s="12">
-        <v>20250520</v>
-      </c>
-      <c r="E30" s="12">
-        <v>80525</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G30" s="12">
-        <v>3</v>
-      </c>
-      <c r="H30" s="12"/>
+      <c r="H30" s="5"/>
       <c r="J30" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LOC_0030','회의실 (소)','LOC','20250520','80525','Y','3','');</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LOC_0030','회의실 (소)','Loc','20250520','80525','Y','3','');</v>
       </c>
     </row>
   </sheetData>
@@ -4204,7 +4172,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="8" style="1" width="15.625"/>
     <col bestFit="1" customWidth="1" min="9" max="9" style="1" width="18.5"/>
@@ -5022,85 +4990,85 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="3" style="8" width="17.625"/>
-    <col customWidth="1" min="4" max="4" style="8" width="61.75"/>
-    <col customWidth="1" min="5" max="5" style="8" width="17.8515625"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" style="8" width="17.875"/>
-    <col customWidth="1" min="7" max="9" style="8" width="17.625"/>
-    <col min="10" max="16384" style="8" width="9"/>
+    <col customWidth="1" min="1" max="3" style="1" width="17.625"/>
+    <col customWidth="1" min="4" max="4" style="1" width="61.75"/>
+    <col customWidth="1" min="5" max="5" style="1" width="17.8515625"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" style="1" width="17.875"/>
+    <col customWidth="1" min="7" max="9" style="1" width="17.625"/>
+    <col min="10" max="16384" style="1" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" s="2" customFormat="1">
+      <c r="A1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-    </row>
-    <row r="2" s="9" customFormat="1">
-      <c r="A2" s="11" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" s="2" customFormat="1">
+      <c r="A2" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="12">
+      <c r="G3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="5">
         <v>1</v>
       </c>
-      <c r="I3" s="12"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="14" t="str">
-        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"','"&amp;I3&amp;"');"</f>
+      <c r="I3" s="5"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="6" t="str">
+        <f t="shared" ref="K3:K6" si="8">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"','"&amp;I3&amp;"');"</f>
         <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0001','휴가 신청서','LEAV','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;휴가 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
 	&lt;tbody&gt;
@@ -5155,34 +5123,34 @@
       </c>
     </row>
     <row r="4" ht="16.5" customHeight="1">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="G4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="12">
+      <c r="G4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="5">
         <v>2</v>
       </c>
-      <c r="I4" s="12"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="14" t="str">
-        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A4&amp;"','"&amp;B4&amp;"','"&amp;C4&amp;"','"&amp;D4&amp;"','"&amp;E4&amp;"','"&amp;F4&amp;"','"&amp;G4&amp;"','"&amp;H4&amp;"','"&amp;I4&amp;"');"</f>
+      <c r="I4" s="5"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="6" t="str">
+        <f t="shared" si="8"/>
         <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0002','가지급결의서','EXP','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;가지급결의서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
 	&lt;tbody&gt;
@@ -5239,34 +5207,34 @@
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G5" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="12">
+      <c r="G5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="5">
         <v>3</v>
       </c>
-      <c r="I5" s="12"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="14" t="str">
-        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A5&amp;"','"&amp;B5&amp;"','"&amp;C5&amp;"','"&amp;D5&amp;"','"&amp;E5&amp;"','"&amp;F5&amp;"','"&amp;G5&amp;"','"&amp;H5&amp;"','"&amp;I5&amp;"');"</f>
+      <c r="I5" s="5"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="6" t="str">
+        <f t="shared" si="8"/>
         <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0003','물품반출입 신청서','ITEM','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;물품반출입 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
 	&lt;tbody&gt;
@@ -5323,34 +5291,34 @@
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="G6" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="12">
+      <c r="G6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="5">
         <v>4</v>
       </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="14" t="str">
-        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A6&amp;"','"&amp;B6&amp;"','"&amp;C6&amp;"','"&amp;D6&amp;"','"&amp;E6&amp;"','"&amp;F6&amp;"','"&amp;G6&amp;"','"&amp;H6&amp;"','"&amp;I6&amp;"');"</f>
+      <c r="I6" s="5"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="6" t="str">
+        <f t="shared" si="8"/>
         <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0004','법인카드 정산서','CORP','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;법인카드 정산서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
 	&lt;tbody&gt;
@@ -5407,6 +5375,9 @@
     <row r="7" ht="16.5" customHeight="1"/>
     <row r="9" ht="17.25" customHeight="1"/>
     <row r="10" ht="17.25" customHeight="1"/>
+    <row r="11" ht="14.25">
+      <c r="C11" s="1"/>
+    </row>
     <row r="12" ht="16.5" customHeight="1"/>
     <row r="14" ht="16.5" customHeight="1"/>
   </sheetData>
@@ -5424,122 +5395,125 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col customWidth="1" min="1" max="15" style="8" width="17.625"/>
-    <col min="16" max="16384" style="8" width="9"/>
+    <col customWidth="1" min="1" max="15" style="1" width="17.625"/>
+    <col min="16" max="16384" style="1" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" s="2" customFormat="1">
+      <c r="A1" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-    </row>
-    <row r="2" s="9" customFormat="1">
-      <c r="A2" s="11" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+    </row>
+    <row r="2" s="2" customFormat="1">
+      <c r="A2" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="O2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="5">
         <v>19900101</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="5">
         <v>19901231</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="9">
         <v>0</v>
       </c>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12" t="s">
+      <c r="I3" s="5"/>
+      <c r="J3" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="L3" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="M3" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="N3" s="12">
+      <c r="M3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="5">
         <v>1</v>
       </c>
-      <c r="O3" s="12"/>
-      <c r="Q3" s="14" t="str">
+      <c r="O3" s="5"/>
+      <c r="Q3" s="6" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"','"&amp;I3&amp;"','"&amp;J3&amp;"','"&amp;K3&amp;"','"&amp;L3&amp;"','"&amp;M3&amp;"','"&amp;N3&amp;"','"&amp;O3&amp;"');"</f>
         <v xml:space="preserve">INSERT INTO PROJECT VALUES('PROJ_0001','내부 프로젝트','내부 프로젝트','19900101','19901231','STAT_0020','EMP_0001','0','','EMP_0001','000000','000000','Y','1','');</v>
       </c>
+    </row>
+    <row r="8" ht="13.5">
+      <c r="H8" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
+++ b/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
   <si>
     <t>MENU</t>
   </si>
@@ -294,12 +294,24 @@
     <t>MENU_0030</t>
   </si>
   <si>
+    <t xml:space="preserve">로그 조회</t>
+  </si>
+  <si>
+    <t>intrLogInqy1010.do</t>
+  </si>
+  <si>
+    <t>MENU_0031</t>
+  </si>
+  <si>
     <t xml:space="preserve">쿼리 입력</t>
   </si>
   <si>
     <t>intrQueryInqy1010.do</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>ROLE</t>
   </si>
   <si>
@@ -315,9 +327,6 @@
     <t xml:space="preserve">관리자 권한</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>ROLE_0002</t>
   </si>
   <si>
@@ -594,7 +603,7 @@
     <t xml:space="preserve">휴가 신청서</t>
   </si>
   <si>
-    <t>LEAV</t>
+    <t>Leav</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;휴가 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
@@ -662,7 +671,7 @@
     <t>가지급결의서</t>
   </si>
   <si>
-    <t>EXP</t>
+    <t>Exp</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;가지급결의서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
@@ -732,7 +741,7 @@
     <t xml:space="preserve">물품반출입 신청서</t>
   </si>
   <si>
-    <t>ITEM</t>
+    <t>Item</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;물품반출입 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
@@ -802,7 +811,7 @@
     <t xml:space="preserve">법인카드 정산서</t>
   </si>
   <si>
-    <t>CORP</t>
+    <t>Corp</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;법인카드 정산서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
@@ -954,9 +963,6 @@
     <t>연차</t>
   </si>
   <si>
-    <t>Leav</t>
-  </si>
-  <si>
     <t>LEAV_0020</t>
   </si>
   <si>
@@ -1105,6 +1111,21 @@
   </si>
   <si>
     <t xml:space="preserve">회의실 (소)</t>
+  </si>
+  <si>
+    <t>PROC_0010</t>
+  </si>
+  <si>
+    <t>조회</t>
+  </si>
+  <si>
+    <t>Proc</t>
+  </si>
+  <si>
+    <t>PROC_0020</t>
+  </si>
+  <si>
+    <t>처리</t>
   </si>
 </sst>
 </file>
@@ -1122,7 +1143,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="10.000000"/>
       <color theme="1"/>
       <name val="돋움"/>
@@ -2332,12 +2352,12 @@
         <v>11</v>
       </c>
       <c r="G24" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H24" s="5"/>
       <c r="J24" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0022','1','프로젝트 관리','MENU_0020','intrProjInqy1010.do','Y','23','');</v>
+        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0022','1','프로젝트 관리','MENU_0020','intrProjInqy1010.do','Y','22','');</v>
       </c>
     </row>
     <row r="25">
@@ -2356,12 +2376,12 @@
         <v>11</v>
       </c>
       <c r="G25" s="5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H25" s="5"/>
       <c r="J25" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0023','1','인사정보','','','Y','24','');</v>
+        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0023','1','인사정보','','','Y','23','');</v>
       </c>
     </row>
     <row r="26">
@@ -2384,12 +2404,12 @@
         <v>11</v>
       </c>
       <c r="G26" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H26" s="5"/>
       <c r="J26" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0024','1','사원 관리','MENU_0023','intrEmpInqy1010.do','Y','25','');</v>
+        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0024','1','사원 관리','MENU_0023','intrEmpInqy1010.do','Y','24','');</v>
       </c>
     </row>
     <row r="27">
@@ -2412,12 +2432,12 @@
         <v>11</v>
       </c>
       <c r="G27" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H27" s="5"/>
       <c r="J27" s="6" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A27&amp;"','"&amp;B27&amp;"','"&amp;C27&amp;"','"&amp;D27&amp;"','"&amp;E27&amp;"','"&amp;F27&amp;"','"&amp;G27&amp;"','"&amp;H27&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0025','1','인사 통계','MENU_0023','intrEmpInqy4010.do','Y','26','');</v>
+        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0025','1','인사 통계','MENU_0023','intrEmpInqy4010.do','Y','25','');</v>
       </c>
     </row>
     <row r="28">
@@ -2436,12 +2456,12 @@
         <v>11</v>
       </c>
       <c r="G28" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H28" s="5"/>
       <c r="J28" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0026','1','시스템 관리','','','Y','27','');</v>
+        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0026','1','시스템 관리','','','Y','26','');</v>
       </c>
     </row>
     <row r="29">
@@ -2464,12 +2484,12 @@
         <v>11</v>
       </c>
       <c r="G29" s="5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H29" s="5"/>
       <c r="J29" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0027','1','권한 관리','MENU_0026','intrRoleInqy1010.do','Y','28','');</v>
+        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0027','1','권한 관리','MENU_0026','intrRoleInqy1010.do','Y','27','');</v>
       </c>
     </row>
     <row r="30">
@@ -2492,12 +2512,12 @@
         <v>11</v>
       </c>
       <c r="G30" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H30" s="5"/>
       <c r="J30" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0028','1','메뉴 권한 부여','MENU_0026','intrRoleInqy2010.do','Y','29','');</v>
+        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0028','1','메뉴 권한 부여','MENU_0026','intrRoleInqy2010.do','Y','28','');</v>
       </c>
     </row>
     <row r="31">
@@ -2520,12 +2540,12 @@
         <v>11</v>
       </c>
       <c r="G31" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H31" s="5"/>
       <c r="J31" s="6" t="str">
         <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A31&amp;"','"&amp;B31&amp;"','"&amp;C31&amp;"','"&amp;D31&amp;"','"&amp;E31&amp;"','"&amp;F31&amp;"','"&amp;G31&amp;"','"&amp;H31&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0029','1','사용자 권한 부여','MENU_0026','intrRoleInqy3010.do','Y','30','');</v>
+        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0029','1','사용자 권한 부여','MENU_0026','intrRoleInqy3010.do','Y','29','');</v>
       </c>
     </row>
     <row r="32">
@@ -2548,12 +2568,41 @@
         <v>11</v>
       </c>
       <c r="G32" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H32" s="5"/>
       <c r="J32" s="6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0030','1','쿼리 입력','MENU_0026','intrQueryInqy1010.do','Y','31','');</v>
+        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0030','1','로그 조회','MENU_0026','intrLogInqy1010.do','Y','30','');</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="5">
+        <v>1</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G33" s="5">
+        <v>31</v>
+      </c>
+      <c r="H33" s="5"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="6" t="str">
+        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A33&amp;"','"&amp;B33&amp;"','"&amp;C33&amp;"','"&amp;D33&amp;"','"&amp;E33&amp;"','"&amp;F33&amp;"','"&amp;G33&amp;"','"&amp;H33&amp;"');"</f>
+        <v xml:space="preserve">INSERT INTO MENU VALUES('MENU_0031','1','쿼리 입력','MENU_0026','intrQueryInqy1010.do','Y','31','');</v>
       </c>
     </row>
   </sheetData>
@@ -2569,7 +2618,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="8" style="1" width="17.625"/>
     <col min="9" max="16384" style="1" width="9"/>
@@ -2577,7 +2626,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2589,19 +2638,19 @@
     </row>
     <row r="2" s="2" customFormat="1">
       <c r="A2" s="4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>6</v>
@@ -2615,13 +2664,13 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D3" s="5">
         <v>20250520</v>
@@ -2643,13 +2692,13 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D4" s="5">
         <v>20250520</v>
@@ -2671,13 +2720,13 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D5" s="5">
         <v>20250520</v>
@@ -2699,13 +2748,13 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D6" s="5">
         <v>20250520</v>
@@ -2727,13 +2776,13 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>237</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>234</v>
       </c>
       <c r="D7" s="5">
         <v>20250520</v>
@@ -2755,13 +2804,13 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>241</v>
+        <v>192</v>
       </c>
       <c r="D8" s="5">
         <v>20250520</v>
@@ -2783,13 +2832,13 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>241</v>
+        <v>192</v>
       </c>
       <c r="D9" s="5">
         <v>20250520</v>
@@ -2811,13 +2860,13 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>241</v>
+        <v>192</v>
       </c>
       <c r="D10" s="5">
         <v>20250520</v>
@@ -2839,13 +2888,13 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>241</v>
+        <v>192</v>
       </c>
       <c r="D11" s="5">
         <v>20250520</v>
@@ -2867,13 +2916,13 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>241</v>
+        <v>192</v>
       </c>
       <c r="D12" s="5">
         <v>20250520</v>
@@ -2895,13 +2944,13 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D13" s="5">
         <v>20250520</v>
@@ -2923,13 +2972,13 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="D14" s="5">
         <v>20250520</v>
@@ -2951,13 +3000,13 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D15" s="5">
         <v>20250520</v>
@@ -2979,13 +3028,13 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" s="5">
         <v>20250520</v>
@@ -3007,13 +3056,13 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="D17" s="5">
         <v>20250520</v>
@@ -3035,13 +3084,13 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" s="5">
         <v>20250520</v>
@@ -3063,13 +3112,13 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D19" s="5">
         <v>20250520</v>
@@ -3091,13 +3140,13 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="D20" s="5">
         <v>20250520</v>
@@ -3119,13 +3168,13 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D21" s="5">
         <v>20250520</v>
@@ -3147,13 +3196,13 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>271</v>
       </c>
       <c r="D22" s="5">
         <v>20250520</v>
@@ -3175,13 +3224,13 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D23" s="5">
         <v>20250520</v>
@@ -3203,13 +3252,13 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D24" s="5">
         <v>20250520</v>
@@ -3231,13 +3280,13 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D25" s="5">
         <v>20250520</v>
@@ -3259,13 +3308,13 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="D26" s="5">
         <v>20250520</v>
@@ -3287,13 +3336,13 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D27" s="5">
         <v>20250520</v>
@@ -3315,13 +3364,13 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D28" s="5">
         <v>20250520</v>
@@ -3343,13 +3392,13 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="D29" s="5">
         <v>20250520</v>
@@ -3371,13 +3420,13 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D30" s="5">
         <v>20250520</v>
@@ -3396,6 +3445,74 @@
         <f t="shared" si="10"/>
         <v xml:space="preserve">INSERT INTO COMMCODE VALUES('LOC_0030','회의실 (소)','Loc','20250520','80525','Y','3','');</v>
       </c>
+    </row>
+    <row r="31" ht="16.5">
+      <c r="A31" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D31" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E31" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G31" s="5">
+        <v>1</v>
+      </c>
+      <c r="H31" s="5"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="6" t="str">
+        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A31&amp;"','"&amp;B31&amp;"','"&amp;C31&amp;"','"&amp;D31&amp;"','"&amp;E31&amp;"','"&amp;F31&amp;"','"&amp;G31&amp;"','"&amp;H31&amp;"');"</f>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('PROC_0010','조회','Proc','20250520','80525','Y','1','');</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5">
+      <c r="A32" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D32" s="5">
+        <v>20250520</v>
+      </c>
+      <c r="E32" s="5">
+        <v>80525</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G32" s="5">
+        <v>2</v>
+      </c>
+      <c r="H32" s="5"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="6" t="str">
+        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A32&amp;"','"&amp;B32&amp;"','"&amp;C32&amp;"','"&amp;D32&amp;"','"&amp;E32&amp;"','"&amp;F32&amp;"','"&amp;G32&amp;"','"&amp;H32&amp;"');"</f>
+        <v xml:space="preserve">INSERT INTO COMMCODE VALUES('PROC_0020','처리','Proc','20250520','80525','Y','2','');</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="J34" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3418,7 +3535,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3427,10 +3544,10 @@
     </row>
     <row r="2" s="2" customFormat="1">
       <c r="A2" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>6</v>
@@ -3444,13 +3561,13 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="D3" s="5">
         <v>1</v>
@@ -3463,13 +3580,13 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D4" s="5">
         <v>2</v>
@@ -3501,7 +3618,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3510,7 +3627,7 @@
     </row>
     <row r="2" s="2" customFormat="1">
       <c r="A2" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>1</v>
@@ -3527,13 +3644,13 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D3" s="5">
         <v>1</v>
@@ -3546,13 +3663,13 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D4" s="5">
         <v>2</v>
@@ -3565,13 +3682,13 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D5" s="5">
         <v>3</v>
@@ -3584,13 +3701,13 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D6" s="5">
         <v>4</v>
@@ -3603,13 +3720,13 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D7" s="5">
         <v>5</v>
@@ -3622,13 +3739,13 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D8" s="5">
         <v>6</v>
@@ -3641,13 +3758,13 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D9" s="5">
         <v>7</v>
@@ -3660,13 +3777,13 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D10" s="5">
         <v>8</v>
@@ -3679,13 +3796,13 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D11" s="5">
         <v>9</v>
@@ -3698,13 +3815,13 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D12" s="5">
         <v>10</v>
@@ -3717,13 +3834,13 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D13" s="5">
         <v>11</v>
@@ -3736,13 +3853,13 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D14" s="5">
         <v>12</v>
@@ -3755,13 +3872,13 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D15" s="5">
         <v>13</v>
@@ -3774,13 +3891,13 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D16" s="5">
         <v>14</v>
@@ -3793,13 +3910,13 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>48</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D17" s="5">
         <v>15</v>
@@ -3812,13 +3929,13 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D18" s="5">
         <v>16</v>
@@ -3831,13 +3948,13 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D19" s="5">
         <v>17</v>
@@ -3850,13 +3967,13 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D20" s="5">
         <v>18</v>
@@ -3869,13 +3986,13 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D21" s="5">
         <v>19</v>
@@ -3888,13 +4005,13 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D22" s="5">
         <v>20</v>
@@ -3907,13 +4024,13 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D23" s="5">
         <v>21</v>
@@ -3926,13 +4043,13 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D24" s="5">
         <v>22</v>
@@ -3945,13 +4062,13 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>70</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D25" s="5">
         <v>23</v>
@@ -3964,13 +4081,13 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>71</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D26" s="5">
         <v>24</v>
@@ -3983,32 +4100,32 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D27" s="5">
         <v>25</v>
       </c>
       <c r="E27" s="5"/>
       <c r="G27" s="6" t="str">
-        <f t="shared" ref="G27:G32" si="5">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A27&amp;"','"&amp;B27&amp;"','"&amp;C27&amp;"','"&amp;D27&amp;"','"&amp;E27&amp;"');"</f>
+        <f t="shared" ref="G27:G33" si="5">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A27&amp;"','"&amp;B27&amp;"','"&amp;C27&amp;"','"&amp;D27&amp;"','"&amp;E27&amp;"');"</f>
         <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0025','Y','25','');</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>77</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D28" s="5">
         <v>26</v>
@@ -4021,13 +4138,13 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>79</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D29" s="5">
         <v>27</v>
@@ -4040,13 +4157,13 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D30" s="5">
         <v>28</v>
@@ -4059,13 +4176,13 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D31" s="5">
         <v>29</v>
@@ -4078,13 +4195,13 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>88</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D32" s="5">
         <v>30</v>
@@ -4093,6 +4210,26 @@
       <c r="G32" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0030','Y','30','');</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5">
+      <c r="A33" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" s="5">
+        <v>31</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">INSERT INTO MENU_ROLE VALUES('ROLE_0001','MENU_0031','Y','31','');</v>
       </c>
     </row>
   </sheetData>
@@ -4116,7 +4253,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -4125,10 +4262,10 @@
     </row>
     <row r="2" s="2" customFormat="1">
       <c r="A2" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>6</v>
@@ -4142,10 +4279,10 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>11</v>
@@ -4182,7 +4319,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -4199,74 +4336,74 @@
     </row>
     <row r="2" s="2" customFormat="1">
       <c r="A2" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L3" s="5">
         <v>20230814</v>
@@ -4298,7 +4435,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -4310,19 +4447,19 @@
     </row>
     <row r="2" s="2" customFormat="1">
       <c r="A2" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>6</v>
@@ -4336,17 +4473,17 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5">
         <v>20230814</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>11</v>
@@ -4362,17 +4499,17 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5">
         <v>20230814</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>11</v>
@@ -4388,17 +4525,17 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5">
         <v>20230814</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>11</v>
@@ -4414,17 +4551,17 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5">
         <v>20230814</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>11</v>
@@ -4440,17 +4577,17 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5">
         <v>20230814</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>11</v>
@@ -4466,17 +4603,17 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5">
         <v>20230814</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>11</v>
@@ -4492,17 +4629,17 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5">
         <v>20230814</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>11</v>
@@ -4518,17 +4655,17 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5">
         <v>20230814</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>11</v>
@@ -4544,17 +4681,17 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5">
         <v>20230814</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>11</v>
@@ -4570,17 +4707,17 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5">
         <v>20230814</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>11</v>
@@ -4596,17 +4733,17 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5">
         <v>20230814</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>11</v>
@@ -4622,17 +4759,17 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5">
         <v>20230814</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>11</v>
@@ -4648,17 +4785,17 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5">
         <v>20230814</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>11</v>
@@ -4693,7 +4830,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -4704,16 +4841,16 @@
     </row>
     <row r="2" s="2" customFormat="1">
       <c r="A2" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>6</v>
@@ -4727,16 +4864,16 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C3" s="5">
         <v>20230814</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>11</v>
@@ -4752,16 +4889,16 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C4" s="5">
         <v>20230814</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>11</v>
@@ -4777,16 +4914,16 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C5" s="5">
         <v>20230814</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>11</v>
@@ -4802,16 +4939,16 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C6" s="5">
         <v>20230814</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>11</v>
@@ -4827,16 +4964,16 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C7" s="5">
         <v>20230814</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>11</v>
@@ -4852,16 +4989,16 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C8" s="5">
         <v>20230814</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>11</v>
@@ -4877,16 +5014,16 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C9" s="5">
         <v>20230814</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>11</v>
@@ -4902,16 +5039,16 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C10" s="5">
         <v>20230814</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>11</v>
@@ -4927,16 +5064,16 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C11" s="5">
         <v>20230814</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>11</v>
@@ -4952,16 +5089,16 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C12" s="5">
         <v>20230814</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>11</v>
@@ -5000,7 +5137,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5013,22 +5150,22 @@
     </row>
     <row r="2" s="2" customFormat="1">
       <c r="A2" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>6</v>
@@ -5042,22 +5179,22 @@
     </row>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>11</v>
@@ -5069,7 +5206,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="6" t="str">
         <f t="shared" ref="K3:K6" si="8">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"','"&amp;I3&amp;"');"</f>
-        <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0001','휴가 신청서','LEAV','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;휴가 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+        <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0001','휴가 신청서','Leav','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;휴가 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
 	&lt;tbody&gt;
 		&lt;tr&gt;
@@ -5124,22 +5261,22 @@
     </row>
     <row r="4" ht="16.5" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>11</v>
@@ -5151,7 +5288,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="6" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0002','가지급결의서','EXP','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;가지급결의서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+        <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0002','가지급결의서','Exp','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;가지급결의서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
 	&lt;tbody&gt;
 		&lt;tr&gt;
@@ -5208,22 +5345,22 @@
     </row>
     <row r="5" ht="16.5" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>11</v>
@@ -5235,7 +5372,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="6" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0003','물품반출입 신청서','ITEM','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;물품반출입 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+        <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0003','물품반출입 신청서','Item','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;물품반출입 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
 	&lt;tbody&gt;
 		&lt;tr&gt;
@@ -5292,22 +5429,22 @@
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>11</v>
@@ -5319,7 +5456,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="6" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0004','법인카드 정산서','CORP','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;법인카드 정산서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+        <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0004','법인카드 정산서','Corp','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;법인카드 정산서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
 	&lt;tbody&gt;
 		&lt;tr&gt;
@@ -5401,7 +5538,7 @@
   <sheetData>
     <row r="1" s="2" customFormat="1">
       <c r="A1" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5420,40 +5557,40 @@
     </row>
     <row r="2" s="2" customFormat="1">
       <c r="A2" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>6</v>
@@ -5467,13 +5604,13 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D3" s="5">
         <v>19900101</v>
@@ -5482,23 +5619,23 @@
         <v>19901231</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H3" s="9">
         <v>0</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>11</v>

--- a/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
+++ b/02.프로젝트/01.인트라넷/01.설계/인트라넷 데이터.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="9"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="MENU" sheetId="1" state="visible" r:id="rId2"/>
@@ -608,54 +608,54 @@
   <si>
     <t xml:space="preserve">&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;휴가 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
-	&lt;tbody&gt;
-		&lt;tr&gt;
-			&lt;td style="border-color:#0d0d0d; border-style:solid; border-width:1px; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;소&amp;nbsp; 속&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성&amp;nbsp; 명&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;직&amp;nbsp; 급&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;구 &amp;nbsp;분&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;( ) 연차 ( ) 병가 ( ) 경조휴가 ( ) 반차 ( ) 기타&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;기 &amp;nbsp;간&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 OO월 OO일 ~ OOOO년 OO월 OO일 (O일간)&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp; 사&amp;nbsp; 유&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td colspan="4" style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:317px; width:603px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;위와 같이 휴가를 신청하오니 허락하여 주시기 바랍니다.&lt;/span&gt;&lt;/p&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO월 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO일&lt;/span&gt;&lt;/p&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;p style="margin-left:253px; text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성명 : O&amp;nbsp; O&amp;nbsp; O&amp;nbsp; (인)&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-	&lt;/tbody&gt;
+ &lt;tbody&gt;
+  &lt;tr&gt;
+   &lt;td style="border-color:#0d0d0d; border-style:solid; border-width:1px; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;소&amp;nbsp; 속&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성&amp;nbsp; 명&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;직&amp;nbsp; 급&lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;구 &amp;nbsp;분&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;( ) 연차 ( ) 병가 ( ) 경조휴가 ( ) 반차 ( ) 기타&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;기 &amp;nbsp;간&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 OO월 OO일 ~ OOOO년 OO월 OO일 (O일간)&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-color:currentcolor #0d0d0d #0d0d0d; border-style:none solid solid; border-width:medium 1px 1px; height:57px; text-align:center; width:200px"&gt;사&amp;nbsp; 유&lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td colspan="4" style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:317px; width:603px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;위와 같이 휴가를 신청하오니 허락하여 주시기 바랍니다.&lt;/span&gt;&lt;/p&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO월 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO일&lt;/span&gt;&lt;/p&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;p style="margin-left:253px; text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성명 : O&amp;nbsp; O&amp;nbsp; O&amp;nbsp; (인)&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+ &lt;/tbody&gt;
 &lt;/table&gt;</t>
   </si>
   <si>
@@ -676,56 +676,56 @@
   <si>
     <t xml:space="preserve">&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;가지급결의서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
-	&lt;tbody&gt;
-		&lt;tr&gt;
-			&lt;td style="border-color:#0d0d0d; border-style:solid; border-width:1px; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;소&amp;nbsp; 속&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;성&amp;nbsp; 명&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;직&amp;nbsp; 급&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;청구 금액&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p&gt;&lt;span style="font-size:13.3333px"&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp;일금 (\&amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp;)&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;지급 방법&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;( ) 현금 ( ) 개인카드 ( ) 전도금&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;지급 일자&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 OO월 OO일&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp;사&amp;nbsp; 유&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td colspan="4" style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:317px; width:603px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;위의 금액을 정히 청구하오니 지급하여 주십시오.&lt;/span&gt;&lt;/p&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO월 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO일&lt;/span&gt;&lt;/p&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;p style="margin-left:253px; text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성명 : O&amp;nbsp; O&amp;nbsp; O&amp;nbsp; (인)&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-	&lt;/tbody&gt;
+ &lt;tbody&gt;
+  &lt;tr&gt;
+   &lt;td style="border-color:#0d0d0d; border-style:solid; border-width:1px; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;소&amp;nbsp; 속&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;성&amp;nbsp; 명&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;직&amp;nbsp; 급&lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;청구 금액&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p&gt;&lt;span style="font-size:13.3333px"&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp;일금 (\&amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp;)&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;지급 방법&lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;( ) 현금 ( ) 개인카드 ( ) 전도금&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;지급 일자&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 OO월 OO일&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-color:currentcolor #0d0d0d #0d0d0d; border-style:none solid solid; border-width:medium 1px 1px; height:57px; text-align:center; width:200px"&gt;사&amp;nbsp; 유&lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td colspan="4" style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:317px; width:603px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;위의 금액을 정히 청구하오니 지급하여 주십시오.&lt;/span&gt;&lt;/p&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO월 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO일&lt;/span&gt;&lt;/p&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;p style="margin-left:253px; text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성명 : O&amp;nbsp; O&amp;nbsp; O&amp;nbsp; (인)&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+ &lt;/tbody&gt;
 &lt;/table&gt;</t>
   </si>
   <si>
@@ -744,58 +744,58 @@
     <t>Item</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;물품반출입 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+    <t xml:space="preserve">&lt;p style="text-align:center"&gt;&lt;span style="font-size:21.3333px"&gt;&lt;strong&gt;&amp;nbsp;물품반출입 신청서&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
-	&lt;tbody&gt;
-		&lt;tr&gt;
-			&lt;td style="border-color:#0d0d0d; border-style:solid; border-width:1px; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;소&amp;nbsp; 속&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;성&amp;nbsp; 명&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;직&amp;nbsp; 급&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;구&amp;nbsp; 분&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;물&amp;nbsp; 품&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;반출일&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 OO월 OO일&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp;사&amp;nbsp; 유&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td colspan="4" style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:317px; width:603px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;위와 같이 물품반출입을 신청하오니 허락하여 주시기 바랍니다.&lt;/span&gt;&lt;/p&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO월 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO일&lt;/span&gt;&lt;/p&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;p style="margin-left:253px; text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성명 : O&amp;nbsp; O&amp;nbsp; O&amp;nbsp; (인)&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-	&lt;/tbody&gt;
+ &lt;tbody&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;소&amp;nbsp; 속&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;성&amp;nbsp; 명&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;직&amp;nbsp; 급&lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;구 분&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p&gt;&lt;span style="font-size:13.3333px"&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp;&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;물 품&lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;반출일&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 OO월 OO일&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-color:currentcolor #0d0d0d #0d0d0d; border-style:none solid solid; border-width:medium 1px 1px; height:57px; text-align:center; width:200px"&gt;사&amp;nbsp; 유&lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td colspan="4" style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:317px; width:603px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;위와 같이 물품반출입을 신청하오니 허락하여 주시기 바랍니다.&lt;/span&gt;&lt;/p&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO월 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO일&lt;/span&gt;&lt;/p&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;p style="margin-left:253px; text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성명 : O&amp;nbsp; O&amp;nbsp; O&amp;nbsp; (인)&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+ &lt;/tbody&gt;
 &lt;/table&gt;</t>
   </si>
   <si>
@@ -814,56 +814,58 @@
     <t>Corp</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;법인카드 정산서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
-	&lt;tbody&gt;
-		&lt;tr&gt;
-			&lt;td style="border-color:#0d0d0d; border-style:solid; border-width:1px; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;소&amp;nbsp; 속&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;성&amp;nbsp; 함&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;직&amp;nbsp; 급&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;사용 카드&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" rowspan="1" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;(카드 회사 / 번호)&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;사용 기간&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 OO월 OO일 ~ OOOO년 OO월 OO일&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;&amp;nbsp; 총 사용금액&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;(\&amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; )&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td colspan="4" style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:317px; width:603px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;위와 같이 법인카드 월간 사용금액을 보고하오니 확인하여 주십시오.&lt;/span&gt;&lt;/p&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO월 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO일&lt;/span&gt;&lt;/p&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;p style="margin-left:253px; text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성명 : O&amp;nbsp; O&amp;nbsp; O&amp;nbsp; (인)&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-	&lt;/tbody&gt;
+    <t xml:space="preserve">&lt;p style="text-align:center"&gt;&lt;span style="font-size:21.3333px"&gt;&lt;strong&gt;&amp;nbsp;법인카드 정산서&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+&lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border-color:currentcolor; border-image:none; border-style:none; border-width:medium; width:503px"&gt;
+ &lt;tbody&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;소&amp;nbsp; 속&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;성&amp;nbsp; 명&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;직&amp;nbsp; 급&lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;사용 카드&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" rowspan="1" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp;(카드 회사 / 카드 번호)&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;사용 일자&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 OO월 OO일&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-color:currentcolor #0d0d0d #0d0d0d currentcolor; border-style:none solid solid none; border-width:medium 1px 1px medium; height:57px; text-align:center; width:200px"&gt;사용처&lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-color:currentcolor #0d0d0d #0d0d0d; border-style:none solid solid; border-width:medium 1px 1px; height:57px; text-align:center; width:200px"&gt;&amp;nbsp;사용 목적&lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td colspan="4" style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:317px; width:603px"&gt;
+   &lt;p style="text-align:center"&gt;위와 같이 법인카드 정산 내역을 신청하오니 승인하여 주시기 바랍니다.&lt;/p&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO월 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO일&lt;/span&gt;&lt;/p&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;p style="margin-left:253px; text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성명 : O&amp;nbsp; O&amp;nbsp; O&amp;nbsp; (인)&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+ &lt;/tbody&gt;
 &lt;/table&gt;</t>
   </si>
   <si>
@@ -3274,7 +3276,7 @@
       </c>
       <c r="H24" s="5"/>
       <c r="J24" s="6" t="str">
-        <f t="shared" ref="J24:J30" si="10">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A24&amp;"','"&amp;B24&amp;"','"&amp;C24&amp;"','"&amp;D24&amp;"','"&amp;E24&amp;"','"&amp;F24&amp;"','"&amp;G24&amp;"','"&amp;H24&amp;"');"</f>
+        <f t="shared" ref="J24:J32" si="10">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A24&amp;"','"&amp;B24&amp;"','"&amp;C24&amp;"','"&amp;D24&amp;"','"&amp;E24&amp;"','"&amp;F24&amp;"','"&amp;G24&amp;"','"&amp;H24&amp;"');"</f>
         <v xml:space="preserve">INSERT INTO COMMCODE VALUES('STEP_0040','결재취소','Step','20250520','80525','Y','4','');</v>
       </c>
     </row>
@@ -3471,7 +3473,7 @@
       <c r="H31" s="5"/>
       <c r="I31" s="1"/>
       <c r="J31" s="6" t="str">
-        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A31&amp;"','"&amp;B31&amp;"','"&amp;C31&amp;"','"&amp;D31&amp;"','"&amp;E31&amp;"','"&amp;F31&amp;"','"&amp;G31&amp;"','"&amp;H31&amp;"');"</f>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">INSERT INTO COMMCODE VALUES('PROC_0010','조회','Proc','20250520','80525','Y','1','');</v>
       </c>
     </row>
@@ -3500,7 +3502,7 @@
       <c r="H32" s="5"/>
       <c r="I32" s="1"/>
       <c r="J32" s="6" t="str">
-        <f>"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A32&amp;"','"&amp;B32&amp;"','"&amp;C32&amp;"','"&amp;D32&amp;"','"&amp;E32&amp;"','"&amp;F32&amp;"','"&amp;G32&amp;"','"&amp;H32&amp;"');"</f>
+        <f t="shared" si="10"/>
         <v xml:space="preserve">INSERT INTO COMMCODE VALUES('PROC_0020','처리','Proc','20250520','80525','Y','2','');</v>
       </c>
     </row>
@@ -5208,54 +5210,54 @@
         <f t="shared" ref="K3:K6" si="8">"INSERT INTO "&amp;$A$1&amp;" VALUES('"&amp;A3&amp;"','"&amp;B3&amp;"','"&amp;C3&amp;"','"&amp;D3&amp;"','"&amp;E3&amp;"','"&amp;F3&amp;"','"&amp;G3&amp;"','"&amp;H3&amp;"','"&amp;I3&amp;"');"</f>
         <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0001','휴가 신청서','Leav','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;휴가 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
-	&lt;tbody&gt;
-		&lt;tr&gt;
-			&lt;td style="border-color:#0d0d0d; border-style:solid; border-width:1px; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;소&amp;nbsp; 속&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성&amp;nbsp; 명&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;직&amp;nbsp; 급&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;구 &amp;nbsp;분&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;( ) 연차 ( ) 병가 ( ) 경조휴가 ( ) 반차 ( ) 기타&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;기 &amp;nbsp;간&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 OO월 OO일 ~ OOOO년 OO월 OO일 (O일간)&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp; 사&amp;nbsp; 유&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td colspan="4" style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:317px; width:603px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;위와 같이 휴가를 신청하오니 허락하여 주시기 바랍니다.&lt;/span&gt;&lt;/p&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO월 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO일&lt;/span&gt;&lt;/p&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;p style="margin-left:253px; text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성명 : O&amp;nbsp; O&amp;nbsp; O&amp;nbsp; (인)&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-	&lt;/tbody&gt;
+ &lt;tbody&gt;
+  &lt;tr&gt;
+   &lt;td style="border-color:#0d0d0d; border-style:solid; border-width:1px; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;소&amp;nbsp; 속&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성&amp;nbsp; 명&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;직&amp;nbsp; 급&lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;구 &amp;nbsp;분&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;( ) 연차 ( ) 병가 ( ) 경조휴가 ( ) 반차 ( ) 기타&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;기 &amp;nbsp;간&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 OO월 OO일 ~ OOOO년 OO월 OO일 (O일간)&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-color:currentcolor #0d0d0d #0d0d0d; border-style:none solid solid; border-width:medium 1px 1px; height:57px; text-align:center; width:200px"&gt;사&amp;nbsp; 유&lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td colspan="4" style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:317px; width:603px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;위와 같이 휴가를 신청하오니 허락하여 주시기 바랍니다.&lt;/span&gt;&lt;/p&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO월 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO일&lt;/span&gt;&lt;/p&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;p style="margin-left:253px; text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성명 : O&amp;nbsp; O&amp;nbsp; O&amp;nbsp; (인)&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+ &lt;/tbody&gt;
 &lt;/table&gt;','intrAprvInqy1020.do','intrAprvInqy2020.do','Y','1','');</v>
       </c>
     </row>
@@ -5290,56 +5292,56 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0002','가지급결의서','Exp','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;가지급결의서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
-	&lt;tbody&gt;
-		&lt;tr&gt;
-			&lt;td style="border-color:#0d0d0d; border-style:solid; border-width:1px; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;소&amp;nbsp; 속&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;성&amp;nbsp; 명&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;직&amp;nbsp; 급&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;청구 금액&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p&gt;&lt;span style="font-size:13.3333px"&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp;일금 (\&amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp;)&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;지급 방법&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;( ) 현금 ( ) 개인카드 ( ) 전도금&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;지급 일자&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 OO월 OO일&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp;사&amp;nbsp; 유&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td colspan="4" style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:317px; width:603px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;위의 금액을 정히 청구하오니 지급하여 주십시오.&lt;/span&gt;&lt;/p&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO월 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO일&lt;/span&gt;&lt;/p&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;p style="margin-left:253px; text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성명 : O&amp;nbsp; O&amp;nbsp; O&amp;nbsp; (인)&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-	&lt;/tbody&gt;
+ &lt;tbody&gt;
+  &lt;tr&gt;
+   &lt;td style="border-color:#0d0d0d; border-style:solid; border-width:1px; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;소&amp;nbsp; 속&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;성&amp;nbsp; 명&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;직&amp;nbsp; 급&lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;청구 금액&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p&gt;&lt;span style="font-size:13.3333px"&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp;일금 (\&amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp;)&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;지급 방법&lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;( ) 현금 ( ) 개인카드 ( ) 전도금&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;지급 일자&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 OO월 OO일&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-color:currentcolor #0d0d0d #0d0d0d; border-style:none solid solid; border-width:medium 1px 1px; height:57px; text-align:center; width:200px"&gt;사&amp;nbsp; 유&lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td colspan="4" style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:317px; width:603px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;위의 금액을 정히 청구하오니 지급하여 주십시오.&lt;/span&gt;&lt;/p&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO월 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO일&lt;/span&gt;&lt;/p&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;p style="margin-left:253px; text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성명 : O&amp;nbsp; O&amp;nbsp; O&amp;nbsp; (인)&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+ &lt;/tbody&gt;
 &lt;/table&gt;','intrAprvInqy1021.do','intrAprvInqy2021.do','Y','2','');</v>
       </c>
     </row>
@@ -5372,58 +5374,58 @@
       <c r="J5" s="1"/>
       <c r="K5" s="6" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0003','물품반출입 신청서','Item','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;물품반출입 신청서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+        <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0003','물품반출입 신청서','Item','&lt;p style="text-align:center"&gt;&lt;span style="font-size:21.3333px"&gt;&lt;strong&gt;&amp;nbsp;물품반출입 신청서&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
 &lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
-	&lt;tbody&gt;
-		&lt;tr&gt;
-			&lt;td style="border-color:#0d0d0d; border-style:solid; border-width:1px; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;소&amp;nbsp; 속&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;성&amp;nbsp; 명&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;직&amp;nbsp; 급&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;구&amp;nbsp; 분&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;물&amp;nbsp; 품&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;반출일&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 OO월 OO일&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp;사&amp;nbsp; 유&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td colspan="4" style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:317px; width:603px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;위와 같이 물품반출입을 신청하오니 허락하여 주시기 바랍니다.&lt;/span&gt;&lt;/p&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO월 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO일&lt;/span&gt;&lt;/p&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;p style="margin-left:253px; text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성명 : O&amp;nbsp; O&amp;nbsp; O&amp;nbsp; (인)&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-	&lt;/tbody&gt;
+ &lt;tbody&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;소&amp;nbsp; 속&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;성&amp;nbsp; 명&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;직&amp;nbsp; 급&lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;구 분&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p&gt;&lt;span style="font-size:13.3333px"&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp;&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;물 품&lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;반출일&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 OO월 OO일&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-color:currentcolor #0d0d0d #0d0d0d; border-style:none solid solid; border-width:medium 1px 1px; height:57px; text-align:center; width:200px"&gt;사&amp;nbsp; 유&lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td colspan="4" style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:317px; width:603px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;위와 같이 물품반출입을 신청하오니 허락하여 주시기 바랍니다.&lt;/span&gt;&lt;/p&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO월 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO일&lt;/span&gt;&lt;/p&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;p style="margin-left:253px; text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성명 : O&amp;nbsp; O&amp;nbsp; O&amp;nbsp; (인)&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+ &lt;/tbody&gt;
 &lt;/table&gt;','intrAprvInqy1022.do','intrAprvInqy2022.do','Y','3','');</v>
       </c>
     </row>
@@ -5456,56 +5458,58 @@
       <c r="J6" s="1"/>
       <c r="K6" s="6" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0004','법인카드 정산서','Corp','&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;&lt;strong&gt;&lt;span style="font-size:16.0pt"&gt;법인카드 정산서&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border:none; width:603px"&gt;
-	&lt;tbody&gt;
-		&lt;tr&gt;
-			&lt;td style="border-color:#0d0d0d; border-style:solid; border-width:1px; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;소&amp;nbsp; 속&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;성&amp;nbsp; 함&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;직&amp;nbsp; 급&lt;/td&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;사용 카드&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" rowspan="1" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;(카드 회사 / 번호)&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;사용 기간&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 OO월 OO일 ~ OOOO년 OO월 OO일&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;&amp;nbsp; 총 사용금액&lt;/td&gt;
-			&lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;(\&amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp; )&lt;/td&gt;
-		&lt;/tr&gt;
-		&lt;tr&gt;
-			&lt;td colspan="4" style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:317px; width:603px"&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;위와 같이 법인카드 월간 사용금액을 보고하오니 확인하여 주십시오.&lt;/span&gt;&lt;/p&gt;
-			&lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO월 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO일&lt;/span&gt;&lt;/p&gt;
-			&lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
-			&lt;p style="margin-left:253px; text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성명 : O&amp;nbsp; O&amp;nbsp; O&amp;nbsp; (인)&lt;/span&gt;&lt;/p&gt;
-			&lt;/td&gt;
-		&lt;/tr&gt;
-	&lt;/tbody&gt;
+        <v xml:space="preserve">INSERT INTO TEMPLATE VALUES('TEMP_0004','법인카드 정산서','Corp','&lt;p style="text-align:center"&gt;&lt;span style="font-size:21.3333px"&gt;&lt;strong&gt;&amp;nbsp;법인카드 정산서&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;
+&lt;table align="center" cellspacing="0" class="MsoTableGrid" style="border-collapse:collapse; border-color:currentcolor; border-image:none; border-style:none; border-width:medium; width:503px"&gt;
+ &lt;tbody&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;소&amp;nbsp; 속&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:1px solid #0d0d0d; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;성&amp;nbsp; 명&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:200px"&gt;직&amp;nbsp; 급&lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;사용 카드&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td colspan="3" rowspan="1" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p&gt;&amp;nbsp; &amp;nbsp; &amp;nbsp;(카드 회사 / 카드 번호)&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:200px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:13.3333px"&gt;사용 일자&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 OO월 OO일&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+   &lt;td style="border-color:currentcolor #0d0d0d #0d0d0d currentcolor; border-style:none solid solid none; border-width:medium 1px 1px medium; height:57px; text-align:center; width:200px"&gt;사용처&lt;/td&gt;
+   &lt;td style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td style="border-color:currentcolor #0d0d0d #0d0d0d; border-style:none solid solid; border-width:medium 1px 1px; height:57px; text-align:center; width:200px"&gt;&amp;nbsp;사용 목적&lt;/td&gt;
+   &lt;td colspan="3" style="border-bottom:1px solid #0d0d0d; border-left:none; border-right:1px solid #0d0d0d; border-top:none; height:57px; text-align:center; width:518px"&gt;&amp;nbsp;&lt;/td&gt;
+  &lt;/tr&gt;
+  &lt;tr&gt;
+   &lt;td colspan="4" style="border-bottom:1px solid #0d0d0d; border-left:1px solid #0d0d0d; border-right:1px solid #0d0d0d; border-top:none; height:317px; width:603px"&gt;
+   &lt;p style="text-align:center"&gt;위와 같이 법인카드 정산 내역을 신청하오니 승인하여 주시기 바랍니다.&lt;/p&gt;
+   &lt;p style="text-align:center"&gt;&lt;span style="font-size:10pt"&gt;OOOO년 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO월 &amp;nbsp;&amp;nbsp;&amp;nbsp;OO일&lt;/span&gt;&lt;/p&gt;
+   &lt;p style="text-align:center"&gt;&amp;nbsp;&lt;/p&gt;
+   &lt;p style="margin-left:253px; text-align:center"&gt;&lt;span style="font-size:10pt"&gt;성명 : O&amp;nbsp; O&amp;nbsp; O&amp;nbsp; (인)&lt;/span&gt;&lt;/p&gt;
+   &lt;/td&gt;
+  &lt;/tr&gt;
+ &lt;/tbody&gt;
 &lt;/table&gt;','intrAprvInqy1023.do','intrAprvInqy2023.do','Y','4','');</v>
       </c>
     </row>
